--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123039744</v>
+        <v>123057570</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>97311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,41 +813,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493408</v>
+        <v>493373</v>
       </c>
       <c r="R3" t="n">
-        <v>7009898</v>
+        <v>7009844</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,26 +896,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123057570</v>
+        <v>123039744</v>
       </c>
       <c r="B4" t="n">
-        <v>97311</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,46 +925,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493373</v>
+        <v>493408</v>
       </c>
       <c r="R4" t="n">
-        <v>7009844</v>
+        <v>7009898</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,6 +1003,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123055266</v>
+        <v>123037385</v>
       </c>
       <c r="B5" t="n">
-        <v>100623</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,31 +1052,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1090,13 +1094,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493376</v>
+        <v>493280</v>
       </c>
       <c r="R5" t="n">
-        <v>7009926</v>
+        <v>7009843</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,6 +1130,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1289,10 +1298,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123037385</v>
+        <v>123055266</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>100623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,35 +1310,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1343,13 +1348,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493280</v>
+        <v>493376</v>
       </c>
       <c r="R7" t="n">
-        <v>7009843</v>
+        <v>7009926</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,11 +1384,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1541,7 +1541,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123052532</v>
+        <v>123047267</v>
       </c>
       <c r="B9" t="n">
         <v>90962</v>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493540</v>
+        <v>493446</v>
       </c>
       <c r="R9" t="n">
-        <v>7009891</v>
+        <v>7009806</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123047267</v>
+        <v>123052532</v>
       </c>
       <c r="B10" t="n">
         <v>90962</v>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493446</v>
+        <v>493540</v>
       </c>
       <c r="R10" t="n">
-        <v>7009806</v>
+        <v>7009891</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123041637</v>
+        <v>123057555</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1967,37 +1967,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493411</v>
+        <v>493366</v>
       </c>
       <c r="R12" t="n">
-        <v>7009877</v>
+        <v>7009842</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2031,7 +2045,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,26 +2060,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2083,10 +2077,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123057555</v>
+        <v>123041637</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2099,51 +2093,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493366</v>
+        <v>493411</v>
       </c>
       <c r="R13" t="n">
-        <v>7009842</v>
+        <v>7009877</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2177,7 +2157,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,6 +2172,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123046343</v>
+        <v>123052141</v>
       </c>
       <c r="B21" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3134,42 +3134,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493442</v>
+        <v>493514</v>
       </c>
       <c r="R21" t="n">
-        <v>7009799</v>
+        <v>7009883</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3203,7 +3198,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3232,12 +3227,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3255,10 +3250,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123052141</v>
+        <v>123046343</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3271,37 +3266,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493514</v>
+        <v>493442</v>
       </c>
       <c r="R22" t="n">
-        <v>7009883</v>
+        <v>7009799</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123037385</v>
+        <v>123055266</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>100623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,35 +1052,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1094,13 +1090,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493280</v>
+        <v>493376</v>
       </c>
       <c r="R5" t="n">
-        <v>7009843</v>
+        <v>7009926</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,11 +1126,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123053948</v>
+        <v>123037385</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,37 +1173,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493492</v>
+        <v>493280</v>
       </c>
       <c r="R6" t="n">
-        <v>7009923</v>
+        <v>7009843</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,7 +1251,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,26 +1266,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1298,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123055266</v>
+        <v>123053948</v>
       </c>
       <c r="B7" t="n">
-        <v>100623</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,48 +1295,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493376</v>
+        <v>493492</v>
       </c>
       <c r="R7" t="n">
-        <v>7009926</v>
+        <v>7009923</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1386,6 +1361,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1398,6 +1378,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123047267</v>
+        <v>123052532</v>
       </c>
       <c r="B9" t="n">
         <v>90962</v>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493446</v>
+        <v>493540</v>
       </c>
       <c r="R9" t="n">
-        <v>7009806</v>
+        <v>7009891</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123052532</v>
+        <v>123047267</v>
       </c>
       <c r="B10" t="n">
         <v>90962</v>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493540</v>
+        <v>493446</v>
       </c>
       <c r="R10" t="n">
-        <v>7009891</v>
+        <v>7009806</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123052756</v>
+        <v>123054425</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493511</v>
+        <v>493457</v>
       </c>
       <c r="R17" t="n">
-        <v>7009902</v>
+        <v>7009914</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en undertryckt döende gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123054425</v>
+        <v>123052756</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493457</v>
+        <v>493511</v>
       </c>
       <c r="R18" t="n">
-        <v>7009914</v>
+        <v>7009902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en undertryckt döende gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123056726</v>
+        <v>123049318</v>
       </c>
       <c r="B19" t="n">
-        <v>91637</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,46 +2866,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493365</v>
+        <v>493450</v>
       </c>
       <c r="R19" t="n">
-        <v>7009914</v>
+        <v>7009784</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2937,6 +2932,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2963,12 +2963,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123049318</v>
+        <v>123046343</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3002,37 +3002,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493450</v>
+        <v>493442</v>
       </c>
       <c r="R20" t="n">
-        <v>7009784</v>
+        <v>7009799</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3066,7 +3071,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3095,12 +3100,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3250,10 +3255,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123046343</v>
+        <v>123034217</v>
       </c>
       <c r="B22" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3266,42 +3271,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493442</v>
+        <v>493321</v>
       </c>
       <c r="R22" t="n">
-        <v>7009799</v>
+        <v>7009835</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3333,11 +3333,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3364,12 +3359,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3387,10 +3382,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123034217</v>
+        <v>123039688</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3403,37 +3398,51 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493321</v>
+        <v>493434</v>
       </c>
       <c r="R23" t="n">
-        <v>7009835</v>
+        <v>7009876</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3465,6 +3474,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3491,12 +3505,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3514,10 +3528,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123039688</v>
+        <v>123048347</v>
       </c>
       <c r="B24" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3530,33 +3544,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3568,13 +3573,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493434</v>
+        <v>493416</v>
       </c>
       <c r="R24" t="n">
-        <v>7009876</v>
+        <v>7009768</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3606,11 +3611,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123048347</v>
+        <v>123041745</v>
       </c>
       <c r="B26" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3837,13 +3837,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493416</v>
+        <v>493424</v>
       </c>
       <c r="R26" t="n">
-        <v>7009768</v>
+        <v>7009866</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123041745</v>
+        <v>123047649</v>
       </c>
       <c r="B27" t="n">
         <v>90962</v>
@@ -3969,13 +3969,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493424</v>
+        <v>493432</v>
       </c>
       <c r="R27" t="n">
-        <v>7009866</v>
+        <v>7009795</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4005,6 +4005,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer i en relativt grov stående döende gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4056,10 +4061,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123047649</v>
+        <v>123049755</v>
       </c>
       <c r="B28" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4072,42 +4077,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493432</v>
+        <v>493474</v>
       </c>
       <c r="R28" t="n">
-        <v>7009795</v>
+        <v>7009808</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4139,11 +4139,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4170,12 +4165,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4193,7 +4188,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123049755</v>
+        <v>123046193</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -4233,13 +4228,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493474</v>
+        <v>493415</v>
       </c>
       <c r="R29" t="n">
-        <v>7009808</v>
+        <v>7009815</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4269,6 +4264,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4320,7 +4320,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123046193</v>
+        <v>123054162</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -4360,13 +4360,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493415</v>
+        <v>493462</v>
       </c>
       <c r="R30" t="n">
-        <v>7009815</v>
+        <v>7009883</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123054162</v>
+        <v>123056726</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>91645</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4464,41 +4464,48 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>493462</v>
+        <v>493365</v>
       </c>
       <c r="R31" t="n">
-        <v>7009883</v>
+        <v>7009914</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4532,7 +4539,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4541,12 +4548,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4566,7 +4574,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4581,6 +4589,141 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123135507</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>493365</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7009914</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123035251</v>
+        <v>123039744</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,51 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493214</v>
+        <v>493408</v>
       </c>
       <c r="R2" t="n">
-        <v>7009801</v>
+        <v>7009898</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,11 +753,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,6 +765,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123057570</v>
+        <v>123050424</v>
       </c>
       <c r="B3" t="n">
-        <v>97311</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,46 +814,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493373</v>
+        <v>493465</v>
       </c>
       <c r="R3" t="n">
-        <v>7009844</v>
+        <v>7009851</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,6 +880,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,6 +897,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123039744</v>
+        <v>123052532</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,37 +950,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493408</v>
+        <v>493540</v>
       </c>
       <c r="R4" t="n">
-        <v>7009898</v>
+        <v>7009891</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,7 +1028,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1017,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1043,7 +1069,7 @@
         <v>123055266</v>
       </c>
       <c r="B5" t="n">
-        <v>100623</v>
+        <v>100631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1157,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123037385</v>
+        <v>123034217</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,51 +1199,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493280</v>
+        <v>493321</v>
       </c>
       <c r="R6" t="n">
-        <v>7009843</v>
+        <v>7009835</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,11 +1261,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1266,6 +1273,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1283,10 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123053948</v>
+        <v>123046087</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,41 +1322,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493492</v>
+        <v>493418</v>
       </c>
       <c r="R7" t="n">
-        <v>7009923</v>
+        <v>7009830</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1363,7 +1395,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+          <t>På en yngre mer smal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,22 +1414,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1415,10 +1447,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123034670</v>
+        <v>123046193</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,51 +1463,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493328</v>
+        <v>493415</v>
       </c>
       <c r="R8" t="n">
-        <v>7009783</v>
+        <v>7009815</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1527,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,6 +1542,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1541,10 +1579,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123052532</v>
+        <v>123035251</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,27 +1595,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1586,13 +1633,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493540</v>
+        <v>493214</v>
       </c>
       <c r="R9" t="n">
-        <v>7009891</v>
+        <v>7009801</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,6 +1671,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1635,27 +1687,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,10 +1705,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123047267</v>
+        <v>123057555</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,27 +1721,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1718,13 +1759,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493446</v>
+        <v>493366</v>
       </c>
       <c r="R10" t="n">
-        <v>7009806</v>
+        <v>7009842</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1756,6 +1797,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1768,26 +1814,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1805,10 +1831,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123037348</v>
+        <v>123052756</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,51 +1847,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493257</v>
+        <v>493511</v>
       </c>
       <c r="R11" t="n">
-        <v>7009814</v>
+        <v>7009902</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1899,7 +1911,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>På en undertryckt döende gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1913,7 +1925,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1928,12 +1940,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1951,10 +1963,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123057555</v>
+        <v>123047895</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>97319</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1963,40 +1975,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2005,10 +2008,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493366</v>
+        <v>493424</v>
       </c>
       <c r="R12" t="n">
-        <v>7009842</v>
+        <v>7009777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2041,11 +2044,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2077,10 +2075,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123041637</v>
+        <v>123037348</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,34 +2091,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493411</v>
+        <v>493257</v>
       </c>
       <c r="R13" t="n">
-        <v>7009877</v>
+        <v>7009814</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2157,7 +2169,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,12 +2198,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2209,10 +2221,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123047895</v>
+        <v>123037385</v>
       </c>
       <c r="B14" t="n">
-        <v>97311</v>
+        <v>57631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,31 +2233,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2254,10 +2275,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493424</v>
+        <v>493280</v>
       </c>
       <c r="R14" t="n">
-        <v>7009777</v>
+        <v>7009843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2290,6 +2311,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2321,10 +2347,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123055634</v>
+        <v>123046343</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2337,34 +2363,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493359</v>
+        <v>493442</v>
       </c>
       <c r="R15" t="n">
-        <v>7009921</v>
+        <v>7009799</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2401,7 +2432,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2420,22 +2451,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2453,10 +2484,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123046087</v>
+        <v>123047649</v>
       </c>
       <c r="B16" t="n">
-        <v>79876</v>
+        <v>90970</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2465,31 +2496,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2498,13 +2529,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493418</v>
+        <v>493432</v>
       </c>
       <c r="R16" t="n">
-        <v>7009830</v>
+        <v>7009795</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2538,7 +2569,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en yngre mer smal sälg.</t>
+          <t>Växer i en relativt grov stående döende gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2557,22 +2588,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2590,10 +2621,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123054425</v>
+        <v>123055634</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2606,21 +2637,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2630,13 +2661,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493457</v>
+        <v>493359</v>
       </c>
       <c r="R17" t="n">
-        <v>7009914</v>
+        <v>7009921</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2670,7 +2701,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2689,22 +2720,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2722,10 +2753,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123052756</v>
+        <v>123057570</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2734,38 +2765,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493511</v>
+        <v>493373</v>
       </c>
       <c r="R18" t="n">
-        <v>7009902</v>
+        <v>7009844</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2800,11 +2836,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en undertryckt döende gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2816,27 +2847,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2986,10 +2997,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123046343</v>
+        <v>123052141</v>
       </c>
       <c r="B20" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3002,42 +3013,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493442</v>
+        <v>493514</v>
       </c>
       <c r="R20" t="n">
-        <v>7009799</v>
+        <v>7009883</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3071,7 +3077,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3100,12 +3106,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3123,10 +3129,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123052141</v>
+        <v>123047267</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3139,37 +3145,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493514</v>
+        <v>493446</v>
       </c>
       <c r="R21" t="n">
-        <v>7009883</v>
+        <v>7009806</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3201,11 +3212,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3232,12 +3238,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3255,10 +3261,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123034217</v>
+        <v>123039688</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3271,37 +3277,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493321</v>
+        <v>493434</v>
       </c>
       <c r="R22" t="n">
-        <v>7009835</v>
+        <v>7009876</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3333,6 +3353,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3359,12 +3384,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3382,10 +3407,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123039688</v>
+        <v>123049755</v>
       </c>
       <c r="B23" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3398,51 +3423,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493434</v>
+        <v>493474</v>
       </c>
       <c r="R23" t="n">
-        <v>7009876</v>
+        <v>7009808</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3474,11 +3485,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3505,12 +3511,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3528,10 +3534,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123048347</v>
+        <v>123041745</v>
       </c>
       <c r="B24" t="n">
-        <v>90944</v>
+        <v>90970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3544,21 +3550,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3573,13 +3579,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493416</v>
+        <v>493424</v>
       </c>
       <c r="R24" t="n">
-        <v>7009768</v>
+        <v>7009866</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3637,12 +3643,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3660,10 +3666,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123050424</v>
+        <v>123048347</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3676,34 +3682,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493465</v>
+        <v>493416</v>
       </c>
       <c r="R25" t="n">
-        <v>7009851</v>
+        <v>7009768</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3738,11 +3749,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3769,12 +3775,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3792,10 +3798,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123041745</v>
+        <v>123053948</v>
       </c>
       <c r="B26" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3808,42 +3814,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493424</v>
+        <v>493492</v>
       </c>
       <c r="R26" t="n">
-        <v>7009866</v>
+        <v>7009923</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3875,6 +3876,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3901,12 +3907,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3924,10 +3930,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123047649</v>
+        <v>123054425</v>
       </c>
       <c r="B27" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3940,42 +3946,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493432</v>
+        <v>493457</v>
       </c>
       <c r="R27" t="n">
-        <v>7009795</v>
+        <v>7009914</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4009,7 +4010,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4038,12 +4039,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4061,10 +4062,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123049755</v>
+        <v>123034670</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4077,37 +4078,51 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493474</v>
+        <v>493328</v>
       </c>
       <c r="R28" t="n">
-        <v>7009808</v>
+        <v>7009783</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4139,6 +4154,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4151,26 +4171,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4188,7 +4188,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123046193</v>
+        <v>123041637</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -4228,13 +4228,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493415</v>
+        <v>493411</v>
       </c>
       <c r="R29" t="n">
-        <v>7009815</v>
+        <v>7009877</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123056726</v>
+        <v>123135507</v>
       </c>
       <c r="B31" t="n">
-        <v>91645</v>
+        <v>90952</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4464,25 +4464,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynjelägden, Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4505,7 +4505,7 @@
         <v>7009914</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4535,11 +4535,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4569,12 +4564,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4592,10 +4587,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123135507</v>
+        <v>123056726</v>
       </c>
       <c r="B32" t="n">
-        <v>90952</v>
+        <v>91645</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4604,25 +4599,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4635,7 +4630,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4645,7 +4640,7 @@
         <v>7009914</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4675,6 +4670,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123050424</v>
+        <v>123055266</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,41 +814,51 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493465</v>
+        <v>493376</v>
       </c>
       <c r="R3" t="n">
-        <v>7009851</v>
+        <v>7009926</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,11 +890,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -897,26 +902,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123052532</v>
+        <v>123050424</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493540</v>
+        <v>493465</v>
       </c>
       <c r="R4" t="n">
-        <v>7009891</v>
+        <v>7009851</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1017,6 +997,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1028,7 +1013,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1043,12 +1028,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123055266</v>
+        <v>123052532</v>
       </c>
       <c r="B5" t="n">
-        <v>100631</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1078,36 +1063,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1116,13 +1096,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493376</v>
+        <v>493540</v>
       </c>
       <c r="R5" t="n">
-        <v>7009926</v>
+        <v>7009891</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1165,7 +1145,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123057570</v>
+        <v>123049318</v>
       </c>
       <c r="B18" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2765,43 +2765,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493373</v>
+        <v>493450</v>
       </c>
       <c r="R18" t="n">
-        <v>7009844</v>
+        <v>7009784</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2836,6 +2831,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2848,6 +2848,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2865,10 +2885,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123049318</v>
+        <v>123057570</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2877,38 +2897,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493450</v>
+        <v>493373</v>
       </c>
       <c r="R19" t="n">
-        <v>7009784</v>
+        <v>7009844</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2943,11 +2968,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2960,26 +2980,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123048347</v>
+        <v>123053948</v>
       </c>
       <c r="B25" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3682,42 +3682,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493416</v>
+        <v>493492</v>
       </c>
       <c r="R25" t="n">
-        <v>7009768</v>
+        <v>7009923</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3749,6 +3744,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123053948</v>
+        <v>123054425</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493492</v>
+        <v>493457</v>
       </c>
       <c r="R26" t="n">
-        <v>7009923</v>
+        <v>7009914</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3930,10 +3930,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123054425</v>
+        <v>123048347</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3946,37 +3946,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493457</v>
+        <v>493416</v>
       </c>
       <c r="R27" t="n">
-        <v>7009914</v>
+        <v>7009768</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4008,11 +4013,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4062,10 +4062,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123034670</v>
+        <v>123041637</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4078,51 +4078,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493328</v>
+        <v>493411</v>
       </c>
       <c r="R28" t="n">
-        <v>7009783</v>
+        <v>7009877</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4156,7 +4142,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4171,6 +4157,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4188,10 +4194,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123041637</v>
+        <v>123034670</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4204,37 +4210,51 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493411</v>
+        <v>493328</v>
       </c>
       <c r="R29" t="n">
-        <v>7009877</v>
+        <v>7009783</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4268,7 +4288,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4283,26 +4303,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123039744</v>
+        <v>123052756</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493408</v>
+        <v>493511</v>
       </c>
       <c r="R2" t="n">
-        <v>7009898</v>
+        <v>7009902</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +753,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en undertryckt döende gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -802,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123055266</v>
+        <v>123041745</v>
       </c>
       <c r="B3" t="n">
-        <v>100631</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,36 +819,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493376</v>
+        <v>493424</v>
       </c>
       <c r="R3" t="n">
-        <v>7009926</v>
+        <v>7009866</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,6 +902,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123050424</v>
+        <v>123039688</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,37 +955,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493465</v>
+        <v>493434</v>
       </c>
       <c r="R4" t="n">
-        <v>7009851</v>
+        <v>7009876</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1033,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,12 +1062,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1183,7 +1217,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123034217</v>
+        <v>123041637</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1223,13 +1257,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493321</v>
+        <v>493411</v>
       </c>
       <c r="R6" t="n">
-        <v>7009835</v>
+        <v>7009877</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,6 +1293,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,10 +1349,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123046087</v>
+        <v>123034217</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1322,46 +1361,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493418</v>
+        <v>493321</v>
       </c>
       <c r="R7" t="n">
-        <v>7009830</v>
+        <v>7009835</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1393,11 +1427,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På en yngre mer smal sälg.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1414,22 +1443,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1447,10 +1476,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123046193</v>
+        <v>123035251</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1463,37 +1492,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493415</v>
+        <v>493214</v>
       </c>
       <c r="R8" t="n">
-        <v>7009815</v>
+        <v>7009801</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1527,7 +1570,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,26 +1585,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1579,10 +1602,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123035251</v>
+        <v>123052141</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,51 +1618,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493214</v>
+        <v>493514</v>
       </c>
       <c r="R9" t="n">
-        <v>7009801</v>
+        <v>7009883</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1673,7 +1682,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,6 +1697,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1705,10 +1734,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123057555</v>
+        <v>123039744</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1721,51 +1750,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493366</v>
+        <v>493408</v>
       </c>
       <c r="R10" t="n">
-        <v>7009842</v>
+        <v>7009898</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1797,11 +1812,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1814,6 +1824,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1831,10 +1861,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123052756</v>
+        <v>123037385</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1847,34 +1877,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493511</v>
+        <v>493280</v>
       </c>
       <c r="R11" t="n">
-        <v>7009902</v>
+        <v>7009843</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1911,7 +1955,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en undertryckt döende gran.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,27 +1969,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1963,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123047895</v>
+        <v>123049755</v>
       </c>
       <c r="B12" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1975,46 +1999,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493424</v>
+        <v>493474</v>
       </c>
       <c r="R12" t="n">
-        <v>7009777</v>
+        <v>7009808</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2058,6 +2077,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2075,7 +2114,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123037348</v>
+        <v>123047649</v>
       </c>
       <c r="B13" t="n">
         <v>90970</v>
@@ -2108,16 +2147,7 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2129,13 +2159,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493257</v>
+        <v>493432</v>
       </c>
       <c r="R13" t="n">
-        <v>7009814</v>
+        <v>7009795</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2169,7 +2199,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>Växer i en relativt grov stående döende gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2198,12 +2228,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2221,7 +2251,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123037385</v>
+        <v>123034670</v>
       </c>
       <c r="B14" t="n">
         <v>57631</v>
@@ -2256,12 +2286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2275,13 +2305,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493280</v>
+        <v>493328</v>
       </c>
       <c r="R14" t="n">
-        <v>7009843</v>
+        <v>7009783</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2315,7 +2345,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2347,10 +2377,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123046343</v>
+        <v>123047895</v>
       </c>
       <c r="B15" t="n">
-        <v>90952</v>
+        <v>97319</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2359,31 +2389,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2392,13 +2422,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493442</v>
+        <v>493424</v>
       </c>
       <c r="R15" t="n">
-        <v>7009799</v>
+        <v>7009777</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2430,11 +2460,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2447,26 +2472,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2484,10 +2489,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123047649</v>
+        <v>123050424</v>
       </c>
       <c r="B16" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2500,42 +2505,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493432</v>
+        <v>493465</v>
       </c>
       <c r="R16" t="n">
-        <v>7009795</v>
+        <v>7009851</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123055634</v>
+        <v>123046087</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2633,41 +2633,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493359</v>
+        <v>493418</v>
       </c>
       <c r="R17" t="n">
-        <v>7009921</v>
+        <v>7009830</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2701,7 +2706,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
+          <t>På en yngre mer smal sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,10 +2758,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123049318</v>
+        <v>123055266</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2765,41 +2770,51 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493450</v>
+        <v>493376</v>
       </c>
       <c r="R18" t="n">
-        <v>7009784</v>
+        <v>7009926</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2831,11 +2846,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2848,26 +2858,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2885,10 +2875,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123057570</v>
+        <v>123046193</v>
       </c>
       <c r="B19" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2897,46 +2887,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493373</v>
+        <v>493415</v>
       </c>
       <c r="R19" t="n">
-        <v>7009844</v>
+        <v>7009815</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2968,6 +2953,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2980,6 +2970,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2997,7 +3007,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123052141</v>
+        <v>123054425</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -3037,13 +3047,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493514</v>
+        <v>493457</v>
       </c>
       <c r="R20" t="n">
-        <v>7009883</v>
+        <v>7009914</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3106,12 +3116,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3129,10 +3139,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123047267</v>
+        <v>123054162</v>
       </c>
       <c r="B21" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3145,42 +3155,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493446</v>
+        <v>493462</v>
       </c>
       <c r="R21" t="n">
-        <v>7009806</v>
+        <v>7009883</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3212,6 +3217,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3223,7 +3233,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3238,12 +3248,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3261,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123039688</v>
+        <v>123046343</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3277,33 +3287,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3315,13 +3316,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493434</v>
+        <v>493442</v>
       </c>
       <c r="R22" t="n">
-        <v>7009876</v>
+        <v>7009799</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3355,7 +3356,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3384,12 +3385,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3407,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123049755</v>
+        <v>123047267</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3423,34 +3424,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493474</v>
+        <v>493446</v>
       </c>
       <c r="R23" t="n">
-        <v>7009808</v>
+        <v>7009806</v>
       </c>
       <c r="S23" t="n">
         <v>12</v>
@@ -3511,12 +3517,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3534,10 +3540,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123041745</v>
+        <v>123053948</v>
       </c>
       <c r="B24" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3550,42 +3556,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493424</v>
+        <v>493492</v>
       </c>
       <c r="R24" t="n">
-        <v>7009866</v>
+        <v>7009923</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3617,6 +3618,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3643,12 +3649,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3666,7 +3672,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123053948</v>
+        <v>123049318</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3706,13 +3712,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493492</v>
+        <v>493450</v>
       </c>
       <c r="R25" t="n">
-        <v>7009923</v>
+        <v>7009784</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3746,7 +3752,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3798,10 +3804,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123054425</v>
+        <v>123048347</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3814,37 +3820,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493457</v>
+        <v>493416</v>
       </c>
       <c r="R26" t="n">
-        <v>7009914</v>
+        <v>7009768</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3876,11 +3887,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3907,12 +3913,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3930,10 +3936,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123048347</v>
+        <v>123037348</v>
       </c>
       <c r="B27" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3946,24 +3952,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3975,10 +3990,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493416</v>
+        <v>493257</v>
       </c>
       <c r="R27" t="n">
-        <v>7009768</v>
+        <v>7009814</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -4013,6 +4028,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4039,12 +4059,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4062,10 +4082,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123041637</v>
+        <v>123055634</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4078,21 +4098,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4102,10 +4122,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493411</v>
+        <v>493359</v>
       </c>
       <c r="R28" t="n">
-        <v>7009877</v>
+        <v>7009921</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4142,7 +4162,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4161,22 +4181,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4194,7 +4214,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123034670</v>
+        <v>123057555</v>
       </c>
       <c r="B29" t="n">
         <v>57631</v>
@@ -4229,7 +4249,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4248,13 +4268,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493328</v>
+        <v>493366</v>
       </c>
       <c r="R29" t="n">
-        <v>7009783</v>
+        <v>7009842</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4288,7 +4308,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4320,10 +4340,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123054162</v>
+        <v>123057570</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4332,41 +4352,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493462</v>
+        <v>493373</v>
       </c>
       <c r="R30" t="n">
-        <v>7009883</v>
+        <v>7009844</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4398,11 +4423,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4414,27 +4434,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -2377,10 +2377,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123047895</v>
+        <v>123050424</v>
       </c>
       <c r="B15" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2389,46 +2389,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493424</v>
+        <v>493465</v>
       </c>
       <c r="R15" t="n">
-        <v>7009777</v>
+        <v>7009851</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2460,6 +2455,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2472,6 +2472,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2489,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123050424</v>
+        <v>123047895</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2501,41 +2521,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493465</v>
+        <v>493424</v>
       </c>
       <c r="R16" t="n">
-        <v>7009851</v>
+        <v>7009777</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2567,11 +2592,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2584,26 +2604,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123046343</v>
+        <v>123047267</v>
       </c>
       <c r="B22" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3316,13 +3316,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493442</v>
+        <v>493446</v>
       </c>
       <c r="R22" t="n">
-        <v>7009799</v>
+        <v>7009806</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3352,11 +3352,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3408,10 +3403,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123047267</v>
+        <v>123046343</v>
       </c>
       <c r="B23" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3424,21 +3419,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3453,13 +3448,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493446</v>
+        <v>493442</v>
       </c>
       <c r="R23" t="n">
-        <v>7009806</v>
+        <v>7009799</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3489,6 +3484,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -2377,10 +2377,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123050424</v>
+        <v>123047895</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2389,41 +2389,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493465</v>
+        <v>493424</v>
       </c>
       <c r="R15" t="n">
-        <v>7009851</v>
+        <v>7009777</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2455,11 +2460,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2472,26 +2472,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2509,10 +2489,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123047895</v>
+        <v>123050424</v>
       </c>
       <c r="B16" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,46 +2501,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493424</v>
+        <v>493465</v>
       </c>
       <c r="R16" t="n">
-        <v>7009777</v>
+        <v>7009851</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2592,6 +2567,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2604,6 +2584,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123055266</v>
+        <v>123046193</v>
       </c>
       <c r="B18" t="n">
-        <v>100631</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2770,51 +2770,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493376</v>
+        <v>493415</v>
       </c>
       <c r="R18" t="n">
-        <v>7009926</v>
+        <v>7009815</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2846,6 +2836,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2858,6 +2853,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2875,10 +2890,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123046193</v>
+        <v>123055266</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2887,41 +2902,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493415</v>
+        <v>493376</v>
       </c>
       <c r="R19" t="n">
-        <v>7009815</v>
+        <v>7009926</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2953,11 +2978,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2970,26 +2990,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123047267</v>
+        <v>123046343</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3316,13 +3316,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493446</v>
+        <v>493442</v>
       </c>
       <c r="R22" t="n">
-        <v>7009806</v>
+        <v>7009799</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3352,6 +3352,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3403,10 +3408,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123046343</v>
+        <v>123047267</v>
       </c>
       <c r="B23" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3419,21 +3424,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3448,13 +3453,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493442</v>
+        <v>493446</v>
       </c>
       <c r="R23" t="n">
-        <v>7009799</v>
+        <v>7009806</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3484,11 +3489,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123052756</v>
+        <v>123037348</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493511</v>
+        <v>493257</v>
       </c>
       <c r="R2" t="n">
-        <v>7009902</v>
+        <v>7009814</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en undertryckt döende gran.</t>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -784,12 +798,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123041745</v>
+        <v>123057570</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>97319</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,31 +833,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,13 +866,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493424</v>
+        <v>493373</v>
       </c>
       <c r="R3" t="n">
-        <v>7009866</v>
+        <v>7009844</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,26 +916,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123039688</v>
+        <v>123046087</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,40 +945,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -993,13 +978,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493434</v>
+        <v>493418</v>
       </c>
       <c r="R4" t="n">
-        <v>7009876</v>
+        <v>7009830</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1033,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>På en yngre mer smal sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,22 +1037,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1085,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123052532</v>
+        <v>123052756</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1101,42 +1086,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493540</v>
+        <v>493511</v>
       </c>
       <c r="R5" t="n">
-        <v>7009891</v>
+        <v>7009902</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1168,6 +1148,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en undertryckt döende gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1194,12 +1179,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1217,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041637</v>
+        <v>123041745</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,37 +1218,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493411</v>
+        <v>493424</v>
       </c>
       <c r="R6" t="n">
-        <v>7009877</v>
+        <v>7009866</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1295,11 +1285,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1326,12 +1311,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1349,10 +1334,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123034217</v>
+        <v>123037385</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1365,37 +1350,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493321</v>
+        <v>493280</v>
       </c>
       <c r="R7" t="n">
-        <v>7009835</v>
+        <v>7009843</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1427,6 +1426,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1439,26 +1443,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123035251</v>
+        <v>123052141</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1492,51 +1476,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493214</v>
+        <v>493514</v>
       </c>
       <c r="R8" t="n">
-        <v>7009801</v>
+        <v>7009883</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1570,7 +1540,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1585,6 +1555,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1602,10 +1592,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123052141</v>
+        <v>123047895</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1614,41 +1604,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493514</v>
+        <v>493424</v>
       </c>
       <c r="R9" t="n">
-        <v>7009883</v>
+        <v>7009777</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1680,11 +1675,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1697,26 +1687,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1734,7 +1704,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123039744</v>
+        <v>123046193</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1774,10 +1744,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493408</v>
+        <v>493415</v>
       </c>
       <c r="R10" t="n">
-        <v>7009898</v>
+        <v>7009815</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
@@ -1810,6 +1780,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1861,10 +1836,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123037385</v>
+        <v>123039744</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1877,51 +1852,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493280</v>
+        <v>493408</v>
       </c>
       <c r="R11" t="n">
-        <v>7009843</v>
+        <v>7009898</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1953,11 +1914,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1970,6 +1926,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1987,10 +1963,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123049755</v>
+        <v>123047267</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,34 +1979,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493474</v>
+        <v>493446</v>
       </c>
       <c r="R12" t="n">
-        <v>7009808</v>
+        <v>7009806</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
@@ -2091,12 +2072,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2114,10 +2095,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123047649</v>
+        <v>123050424</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2130,42 +2111,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493432</v>
+        <v>493465</v>
       </c>
       <c r="R13" t="n">
-        <v>7009795</v>
+        <v>7009851</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2199,7 +2175,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2228,12 +2204,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2251,10 +2227,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123034670</v>
+        <v>123052532</v>
       </c>
       <c r="B14" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2267,36 +2243,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2305,13 +2272,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493328</v>
+        <v>493540</v>
       </c>
       <c r="R14" t="n">
-        <v>7009783</v>
+        <v>7009891</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2343,11 +2310,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2359,7 +2321,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2377,10 +2359,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123047895</v>
+        <v>123055634</v>
       </c>
       <c r="B15" t="n">
-        <v>97319</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2389,46 +2371,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493424</v>
+        <v>493359</v>
       </c>
       <c r="R15" t="n">
-        <v>7009777</v>
+        <v>7009921</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2460,6 +2437,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2472,6 +2454,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2489,7 +2491,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123050424</v>
+        <v>123054425</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2529,13 +2531,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493465</v>
+        <v>493457</v>
       </c>
       <c r="R16" t="n">
-        <v>7009851</v>
+        <v>7009914</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2621,10 +2623,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123046087</v>
+        <v>123048347</v>
       </c>
       <c r="B17" t="n">
-        <v>79876</v>
+        <v>90952</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2633,31 +2635,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2666,13 +2668,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493418</v>
+        <v>493416</v>
       </c>
       <c r="R17" t="n">
-        <v>7009830</v>
+        <v>7009768</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2704,11 +2706,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en yngre mer smal sälg.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2725,22 +2722,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2758,10 +2755,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123046193</v>
+        <v>123047649</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2774,37 +2771,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493415</v>
+        <v>493432</v>
       </c>
       <c r="R18" t="n">
-        <v>7009815</v>
+        <v>7009795</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2838,7 +2840,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Växer i en relativt grov stående döende gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2867,12 +2869,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2890,10 +2892,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123055266</v>
+        <v>123041637</v>
       </c>
       <c r="B19" t="n">
-        <v>100631</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2902,51 +2904,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493376</v>
+        <v>493411</v>
       </c>
       <c r="R19" t="n">
-        <v>7009926</v>
+        <v>7009877</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2978,6 +2970,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2990,6 +2987,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3007,7 +3024,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123054425</v>
+        <v>123049318</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -3047,10 +3064,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493457</v>
+        <v>493450</v>
       </c>
       <c r="R20" t="n">
-        <v>7009914</v>
+        <v>7009784</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3139,7 +3156,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123054162</v>
+        <v>123049755</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -3179,13 +3196,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493462</v>
+        <v>493474</v>
       </c>
       <c r="R21" t="n">
-        <v>7009883</v>
+        <v>7009808</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3217,11 +3234,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3233,7 +3245,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3248,12 +3260,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3271,10 +3283,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123046343</v>
+        <v>123035251</v>
       </c>
       <c r="B22" t="n">
-        <v>90952</v>
+        <v>57631</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3287,27 +3299,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3316,13 +3337,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493442</v>
+        <v>493214</v>
       </c>
       <c r="R22" t="n">
-        <v>7009799</v>
+        <v>7009801</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3356,7 +3377,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3371,26 +3392,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3408,10 +3409,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123047267</v>
+        <v>123034670</v>
       </c>
       <c r="B23" t="n">
-        <v>90970</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3424,27 +3425,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3453,13 +3463,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493446</v>
+        <v>493328</v>
       </c>
       <c r="R23" t="n">
-        <v>7009806</v>
+        <v>7009783</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3491,6 +3501,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3503,26 +3518,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3540,10 +3535,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123053948</v>
+        <v>123057555</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3556,37 +3551,51 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493492</v>
+        <v>493366</v>
       </c>
       <c r="R24" t="n">
-        <v>7009923</v>
+        <v>7009842</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3620,7 +3629,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3635,26 +3644,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3672,7 +3661,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123049318</v>
+        <v>123034217</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3712,13 +3701,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493450</v>
+        <v>493321</v>
       </c>
       <c r="R25" t="n">
-        <v>7009784</v>
+        <v>7009835</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3748,11 +3737,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3804,10 +3788,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123048347</v>
+        <v>123053948</v>
       </c>
       <c r="B26" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3820,42 +3804,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493416</v>
+        <v>493492</v>
       </c>
       <c r="R26" t="n">
-        <v>7009768</v>
+        <v>7009923</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3887,6 +3866,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3913,12 +3897,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3936,10 +3920,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123037348</v>
+        <v>123054162</v>
       </c>
       <c r="B27" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3952,51 +3936,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493257</v>
+        <v>493462</v>
       </c>
       <c r="R27" t="n">
-        <v>7009814</v>
+        <v>7009883</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4030,7 +4000,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4044,7 +4014,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4082,10 +4052,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123055634</v>
+        <v>123046343</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4098,34 +4068,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493359</v>
+        <v>493442</v>
       </c>
       <c r="R28" t="n">
-        <v>7009921</v>
+        <v>7009799</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4162,7 +4137,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4181,22 +4156,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4214,10 +4189,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123057555</v>
+        <v>123039688</v>
       </c>
       <c r="B29" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4230,36 +4205,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4268,13 +4243,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493366</v>
+        <v>493434</v>
       </c>
       <c r="R29" t="n">
-        <v>7009842</v>
+        <v>7009876</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4308,7 +4283,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4323,6 +4298,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4340,10 +4335,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123057570</v>
+        <v>123055266</v>
       </c>
       <c r="B30" t="n">
-        <v>97319</v>
+        <v>100631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4356,21 +4351,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4379,19 +4374,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493373</v>
+        <v>493376</v>
       </c>
       <c r="R30" t="n">
-        <v>7009844</v>
+        <v>7009926</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123037348</v>
+        <v>123037385</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493257</v>
+        <v>493280</v>
       </c>
       <c r="R2" t="n">
-        <v>7009814</v>
+        <v>7009843</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,26 +784,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -821,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123057570</v>
+        <v>123041637</v>
       </c>
       <c r="B3" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,46 +813,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493373</v>
+        <v>493411</v>
       </c>
       <c r="R3" t="n">
-        <v>7009844</v>
+        <v>7009877</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,6 +879,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -916,6 +896,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123046087</v>
+        <v>123054425</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,46 +945,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493418</v>
+        <v>493457</v>
       </c>
       <c r="R4" t="n">
-        <v>7009830</v>
+        <v>7009914</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en yngre mer smal sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,22 +1032,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1070,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123052756</v>
+        <v>123035251</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,37 +1081,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493511</v>
+        <v>493214</v>
       </c>
       <c r="R5" t="n">
-        <v>7009902</v>
+        <v>7009801</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1150,7 +1159,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en undertryckt döende gran.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,27 +1173,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041745</v>
+        <v>123054162</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,42 +1207,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493424</v>
+        <v>493462</v>
       </c>
       <c r="R6" t="n">
-        <v>7009866</v>
+        <v>7009883</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1285,6 +1269,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1296,7 +1285,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1311,12 +1300,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,10 +1323,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123037385</v>
+        <v>123039688</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,36 +1339,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1388,13 +1377,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493280</v>
+        <v>493434</v>
       </c>
       <c r="R7" t="n">
-        <v>7009843</v>
+        <v>7009876</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1428,7 +1417,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,6 +1432,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1460,7 +1469,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123052141</v>
+        <v>123039744</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1500,13 +1509,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493514</v>
+        <v>493408</v>
       </c>
       <c r="R8" t="n">
-        <v>7009883</v>
+        <v>7009898</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1538,11 +1547,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1569,12 +1573,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1592,10 +1596,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123047895</v>
+        <v>123034670</v>
       </c>
       <c r="B9" t="n">
-        <v>97319</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1604,31 +1608,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1637,13 +1650,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493424</v>
+        <v>493328</v>
       </c>
       <c r="R9" t="n">
-        <v>7009777</v>
+        <v>7009783</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1673,6 +1686,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1704,10 +1722,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123046193</v>
+        <v>123037348</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1720,37 +1738,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493415</v>
+        <v>493257</v>
       </c>
       <c r="R10" t="n">
-        <v>7009815</v>
+        <v>7009814</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1784,7 +1816,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1813,12 +1845,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1836,10 +1868,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123039744</v>
+        <v>123055634</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1852,21 +1884,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1876,13 +1908,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493408</v>
+        <v>493359</v>
       </c>
       <c r="R11" t="n">
-        <v>7009898</v>
+        <v>7009921</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1914,6 +1946,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1930,22 +1967,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1963,10 +2000,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123047267</v>
+        <v>123047895</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>97319</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1975,31 +2012,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2008,13 +2045,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493446</v>
+        <v>493424</v>
       </c>
       <c r="R12" t="n">
-        <v>7009806</v>
+        <v>7009777</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2058,26 +2095,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2227,10 +2244,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123052532</v>
+        <v>123052141</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2243,42 +2260,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493540</v>
+        <v>493514</v>
       </c>
       <c r="R14" t="n">
-        <v>7009891</v>
+        <v>7009883</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2310,6 +2322,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2321,7 +2338,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2359,10 +2376,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123055634</v>
+        <v>123046193</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2375,21 +2392,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2399,13 +2416,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493359</v>
+        <v>493415</v>
       </c>
       <c r="R15" t="n">
-        <v>7009921</v>
+        <v>7009815</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2439,7 +2456,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2458,22 +2475,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2491,7 +2508,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123054425</v>
+        <v>123049755</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2531,13 +2548,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493457</v>
+        <v>493474</v>
       </c>
       <c r="R16" t="n">
-        <v>7009914</v>
+        <v>7009808</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2567,11 +2584,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2623,10 +2635,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123048347</v>
+        <v>123057555</v>
       </c>
       <c r="B17" t="n">
-        <v>90952</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2639,27 +2651,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2668,13 +2689,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493416</v>
+        <v>493366</v>
       </c>
       <c r="R17" t="n">
-        <v>7009768</v>
+        <v>7009842</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2706,6 +2727,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2718,26 +2744,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2755,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123047649</v>
+        <v>123046343</v>
       </c>
       <c r="B18" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2771,21 +2777,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2800,13 +2806,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493432</v>
+        <v>493442</v>
       </c>
       <c r="R18" t="n">
-        <v>7009795</v>
+        <v>7009799</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2840,7 +2846,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2869,12 +2875,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,7 +2898,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123041637</v>
+        <v>123034217</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2932,13 +2938,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493411</v>
+        <v>493321</v>
       </c>
       <c r="R19" t="n">
-        <v>7009877</v>
+        <v>7009835</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2968,11 +2974,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3024,10 +3025,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123049318</v>
+        <v>123055266</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>100631</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3036,41 +3037,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493450</v>
+        <v>493376</v>
       </c>
       <c r="R20" t="n">
-        <v>7009784</v>
+        <v>7009926</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3102,11 +3113,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3119,26 +3125,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3156,10 +3142,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123049755</v>
+        <v>123041745</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3172,37 +3158,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493474</v>
+        <v>493424</v>
       </c>
       <c r="R21" t="n">
-        <v>7009808</v>
+        <v>7009866</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3260,12 +3251,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3283,10 +3274,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123035251</v>
+        <v>123048347</v>
       </c>
       <c r="B22" t="n">
-        <v>57631</v>
+        <v>90952</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3299,36 +3290,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3337,13 +3319,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493214</v>
+        <v>493416</v>
       </c>
       <c r="R22" t="n">
-        <v>7009801</v>
+        <v>7009768</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3375,11 +3357,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3392,6 +3369,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3409,10 +3406,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123034670</v>
+        <v>123057570</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>97319</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3421,40 +3418,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3463,13 +3451,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493328</v>
+        <v>493373</v>
       </c>
       <c r="R23" t="n">
-        <v>7009783</v>
+        <v>7009844</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3499,11 +3487,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3535,10 +3518,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123057555</v>
+        <v>123047267</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3551,36 +3534,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3589,13 +3563,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493366</v>
+        <v>493446</v>
       </c>
       <c r="R24" t="n">
-        <v>7009842</v>
+        <v>7009806</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3627,11 +3601,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3644,6 +3613,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3661,7 +3650,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123034217</v>
+        <v>123049318</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3701,13 +3690,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493321</v>
+        <v>493450</v>
       </c>
       <c r="R25" t="n">
-        <v>7009835</v>
+        <v>7009784</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3737,6 +3726,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3788,10 +3782,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123053948</v>
+        <v>123052532</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3804,37 +3798,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493492</v>
+        <v>493540</v>
       </c>
       <c r="R26" t="n">
-        <v>7009923</v>
+        <v>7009891</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3866,11 +3865,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3882,7 +3876,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3897,12 +3891,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3920,7 +3914,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123054162</v>
+        <v>123052756</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3960,13 +3954,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493462</v>
+        <v>493511</v>
       </c>
       <c r="R27" t="n">
-        <v>7009883</v>
+        <v>7009902</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4000,7 +3994,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>På en undertryckt döende gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4029,12 +4023,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4052,10 +4046,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123046343</v>
+        <v>123053948</v>
       </c>
       <c r="B28" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4068,42 +4062,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493442</v>
+        <v>493492</v>
       </c>
       <c r="R28" t="n">
-        <v>7009799</v>
+        <v>7009923</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4137,7 +4126,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4166,12 +4155,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4189,10 +4178,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123039688</v>
+        <v>123046087</v>
       </c>
       <c r="B29" t="n">
-        <v>90970</v>
+        <v>79876</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4201,40 +4190,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4243,13 +4223,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493434</v>
+        <v>493418</v>
       </c>
       <c r="R29" t="n">
-        <v>7009876</v>
+        <v>7009830</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4283,7 +4263,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>På en yngre mer smal sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4302,22 +4282,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4335,10 +4315,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123055266</v>
+        <v>123047649</v>
       </c>
       <c r="B30" t="n">
-        <v>100631</v>
+        <v>90970</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4347,36 +4327,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4385,10 +4360,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493376</v>
+        <v>493432</v>
       </c>
       <c r="R30" t="n">
-        <v>7009926</v>
+        <v>7009795</v>
       </c>
       <c r="S30" t="n">
         <v>8</v>
@@ -4423,6 +4398,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer i en relativt grov stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4435,6 +4415,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123135507</v>
+        <v>123056726</v>
       </c>
       <c r="B31" t="n">
-        <v>90952</v>
+        <v>91645</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4464,25 +4464,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4505,7 +4505,7 @@
         <v>7009914</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4535,6 +4535,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4564,12 +4569,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4587,10 +4592,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123056726</v>
+        <v>123135507</v>
       </c>
       <c r="B32" t="n">
-        <v>91645</v>
+        <v>90952</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4599,25 +4604,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4630,7 +4635,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynjelägden, Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4640,7 +4645,7 @@
         <v>7009914</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4670,11 +4675,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -933,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123054425</v>
+        <v>123035251</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,37 +949,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493457</v>
+        <v>493214</v>
       </c>
       <c r="R4" t="n">
-        <v>7009914</v>
+        <v>7009801</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +1027,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,26 +1042,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1065,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123035251</v>
+        <v>123054425</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,51 +1075,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493214</v>
+        <v>493457</v>
       </c>
       <c r="R5" t="n">
-        <v>7009801</v>
+        <v>7009914</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1159,7 +1139,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,6 +1154,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -933,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123035251</v>
+        <v>123054425</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,51 +949,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493214</v>
+        <v>493457</v>
       </c>
       <c r="R4" t="n">
-        <v>7009801</v>
+        <v>7009914</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,6 +1028,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123054425</v>
+        <v>123035251</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,37 +1081,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493457</v>
+        <v>493214</v>
       </c>
       <c r="R5" t="n">
-        <v>7009914</v>
+        <v>7009801</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,7 +1159,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,26 +1174,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123046343</v>
+        <v>123055266</v>
       </c>
       <c r="B18" t="n">
-        <v>90952</v>
+        <v>100631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2773,31 +2773,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2806,13 +2811,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493442</v>
+        <v>493376</v>
       </c>
       <c r="R18" t="n">
-        <v>7009799</v>
+        <v>7009926</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2844,11 +2849,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2861,26 +2861,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2898,10 +2878,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123034217</v>
+        <v>123046343</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2914,37 +2894,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493321</v>
+        <v>493442</v>
       </c>
       <c r="R19" t="n">
-        <v>7009835</v>
+        <v>7009799</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2976,6 +2961,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3002,12 +2992,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3025,10 +3015,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123055266</v>
+        <v>123034217</v>
       </c>
       <c r="B20" t="n">
-        <v>100631</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3037,48 +3027,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493376</v>
+        <v>493321</v>
       </c>
       <c r="R20" t="n">
-        <v>7009926</v>
+        <v>7009835</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3125,6 +3105,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123037385</v>
+        <v>123057570</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>97322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493280</v>
+        <v>493373</v>
       </c>
       <c r="R2" t="n">
-        <v>7009843</v>
+        <v>7009844</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123041637</v>
+        <v>123048347</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493411</v>
+        <v>493416</v>
       </c>
       <c r="R3" t="n">
-        <v>7009877</v>
+        <v>7009768</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -879,11 +870,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,12 +896,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123035251</v>
+        <v>123052756</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,51 +935,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493214</v>
+        <v>493511</v>
       </c>
       <c r="R4" t="n">
-        <v>7009801</v>
+        <v>7009902</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>På en undertryckt döende gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1013,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,7 +1054,7 @@
         <v>123054425</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1191,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123054162</v>
+        <v>123050424</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1231,13 +1223,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493462</v>
+        <v>493465</v>
       </c>
       <c r="R6" t="n">
-        <v>7009883</v>
+        <v>7009851</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,7 +1263,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,7 +1277,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1300,12 +1292,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1323,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123039688</v>
+        <v>123046087</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>79879</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,40 +1327,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1377,13 +1360,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493434</v>
+        <v>493418</v>
       </c>
       <c r="R7" t="n">
-        <v>7009876</v>
+        <v>7009830</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1417,7 +1400,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>På en yngre mer smal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,22 +1419,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1469,10 +1452,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123039744</v>
+        <v>123055634</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1485,21 +1468,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1509,13 +1492,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493408</v>
+        <v>493359</v>
       </c>
       <c r="R8" t="n">
-        <v>7009898</v>
+        <v>7009921</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1547,6 +1530,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1563,22 +1551,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1596,10 +1584,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123034670</v>
+        <v>123052141</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1612,48 +1600,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493328</v>
+        <v>493514</v>
       </c>
       <c r="R9" t="n">
-        <v>7009783</v>
+        <v>7009883</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1690,7 +1664,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1705,6 +1679,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1722,10 +1716,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123037348</v>
+        <v>123052532</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1755,16 +1749,7 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -1776,10 +1761,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493257</v>
+        <v>493540</v>
       </c>
       <c r="R10" t="n">
-        <v>7009814</v>
+        <v>7009891</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1814,11 +1799,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1830,7 +1810,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1868,10 +1848,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123055634</v>
+        <v>123053948</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1884,21 +1864,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1908,13 +1888,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493359</v>
+        <v>493492</v>
       </c>
       <c r="R11" t="n">
-        <v>7009921</v>
+        <v>7009923</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1948,7 +1928,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,22 +1947,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2000,10 +1980,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123047895</v>
+        <v>123034670</v>
       </c>
       <c r="B12" t="n">
-        <v>97319</v>
+        <v>57634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2012,31 +1992,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2045,13 +2034,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493424</v>
+        <v>493328</v>
       </c>
       <c r="R12" t="n">
-        <v>7009777</v>
+        <v>7009783</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2081,6 +2070,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2112,10 +2106,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123050424</v>
+        <v>123037385</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2128,37 +2122,51 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493465</v>
+        <v>493280</v>
       </c>
       <c r="R13" t="n">
-        <v>7009851</v>
+        <v>7009843</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2192,7 +2200,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2207,26 +2215,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2244,10 +2232,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123052141</v>
+        <v>123049755</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2284,13 +2272,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493514</v>
+        <v>493474</v>
       </c>
       <c r="R14" t="n">
-        <v>7009883</v>
+        <v>7009808</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2322,11 +2310,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2353,12 +2336,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2376,10 +2359,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123046193</v>
+        <v>123039744</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2416,10 +2399,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493415</v>
+        <v>493408</v>
       </c>
       <c r="R15" t="n">
-        <v>7009815</v>
+        <v>7009898</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
@@ -2452,11 +2435,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2508,10 +2486,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123049755</v>
+        <v>123047649</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>90973</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2524,37 +2502,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493474</v>
+        <v>493432</v>
       </c>
       <c r="R16" t="n">
-        <v>7009808</v>
+        <v>7009795</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2586,6 +2569,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer i en relativt grov stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2612,12 +2600,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2635,10 +2623,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123057555</v>
+        <v>123035251</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2689,13 +2677,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493366</v>
+        <v>493214</v>
       </c>
       <c r="R17" t="n">
-        <v>7009842</v>
+        <v>7009801</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2761,10 +2749,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123055266</v>
+        <v>123041745</v>
       </c>
       <c r="B18" t="n">
-        <v>100631</v>
+        <v>90973</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2773,36 +2761,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2811,13 +2794,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493376</v>
+        <v>493424</v>
       </c>
       <c r="R18" t="n">
-        <v>7009926</v>
+        <v>7009866</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2861,6 +2844,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2878,10 +2881,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123046343</v>
+        <v>123034217</v>
       </c>
       <c r="B19" t="n">
-        <v>90952</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2894,42 +2897,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493442</v>
+        <v>493321</v>
       </c>
       <c r="R19" t="n">
-        <v>7009799</v>
+        <v>7009835</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2961,11 +2959,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2992,12 +2985,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3015,10 +3008,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123034217</v>
+        <v>123037348</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>90973</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3031,37 +3024,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493321</v>
+        <v>493257</v>
       </c>
       <c r="R20" t="n">
-        <v>7009835</v>
+        <v>7009814</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3093,6 +3100,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3119,12 +3131,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3142,10 +3154,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123041745</v>
+        <v>123049318</v>
       </c>
       <c r="B21" t="n">
-        <v>90970</v>
+        <v>78769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3158,42 +3170,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493424</v>
+        <v>493450</v>
       </c>
       <c r="R21" t="n">
-        <v>7009866</v>
+        <v>7009784</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3225,6 +3232,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3251,12 +3263,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3274,10 +3286,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123048347</v>
+        <v>123039688</v>
       </c>
       <c r="B22" t="n">
-        <v>90952</v>
+        <v>90973</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3290,24 +3302,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3319,13 +3340,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493416</v>
+        <v>493434</v>
       </c>
       <c r="R22" t="n">
-        <v>7009768</v>
+        <v>7009876</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3357,6 +3378,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3383,12 +3409,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3406,10 +3432,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123057570</v>
+        <v>123055266</v>
       </c>
       <c r="B23" t="n">
-        <v>97319</v>
+        <v>100634</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3422,21 +3448,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3445,19 +3471,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493373</v>
+        <v>493376</v>
       </c>
       <c r="R23" t="n">
-        <v>7009844</v>
+        <v>7009926</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3521,7 +3552,7 @@
         <v>123047267</v>
       </c>
       <c r="B24" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3650,10 +3681,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123049318</v>
+        <v>123046193</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3690,13 +3721,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493450</v>
+        <v>493415</v>
       </c>
       <c r="R25" t="n">
-        <v>7009784</v>
+        <v>7009815</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3782,10 +3813,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123052532</v>
+        <v>123041637</v>
       </c>
       <c r="B26" t="n">
-        <v>90970</v>
+        <v>78769</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3798,39 +3829,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493540</v>
+        <v>493411</v>
       </c>
       <c r="R26" t="n">
-        <v>7009891</v>
+        <v>7009877</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3865,6 +3891,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3876,7 +3907,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3891,12 +3922,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3914,10 +3945,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123052756</v>
+        <v>123054162</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3954,13 +3985,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493511</v>
+        <v>493462</v>
       </c>
       <c r="R27" t="n">
-        <v>7009902</v>
+        <v>7009883</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3994,7 +4025,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en undertryckt döende gran.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4023,12 +4054,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4046,10 +4077,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123053948</v>
+        <v>123046343</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4062,37 +4093,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493492</v>
+        <v>493442</v>
       </c>
       <c r="R28" t="n">
-        <v>7009923</v>
+        <v>7009799</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4126,7 +4162,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4155,12 +4191,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4178,10 +4214,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123046087</v>
+        <v>123047895</v>
       </c>
       <c r="B29" t="n">
-        <v>79876</v>
+        <v>97322</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4194,27 +4230,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4223,13 +4259,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493418</v>
+        <v>493424</v>
       </c>
       <c r="R29" t="n">
-        <v>7009830</v>
+        <v>7009777</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4261,11 +4297,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På en yngre mer smal sälg.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4278,26 +4309,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4315,10 +4326,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123047649</v>
+        <v>123057555</v>
       </c>
       <c r="B30" t="n">
-        <v>90970</v>
+        <v>57634</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4331,27 +4342,36 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4360,13 +4380,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493432</v>
+        <v>493366</v>
       </c>
       <c r="R30" t="n">
-        <v>7009795</v>
+        <v>7009842</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4400,7 +4420,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4415,26 +4435,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123056726</v>
+        <v>123135507</v>
       </c>
       <c r="B31" t="n">
-        <v>91645</v>
+        <v>90955</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4464,25 +4464,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynjelägden, Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4505,7 +4505,7 @@
         <v>7009914</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4535,11 +4535,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4569,12 +4564,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4592,10 +4587,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123135507</v>
+        <v>123056726</v>
       </c>
       <c r="B32" t="n">
-        <v>90952</v>
+        <v>91648</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4604,25 +4599,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4635,7 +4630,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4645,7 +4640,7 @@
         <v>7009914</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4675,6 +4670,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123057570</v>
+        <v>123052141</v>
       </c>
       <c r="B2" t="n">
-        <v>97322</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493373</v>
+        <v>493514</v>
       </c>
       <c r="R2" t="n">
-        <v>7009844</v>
+        <v>7009883</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,6 +753,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,6 +770,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123048347</v>
+        <v>123046343</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493416</v>
+        <v>493442</v>
       </c>
       <c r="R3" t="n">
-        <v>7009768</v>
+        <v>7009799</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -868,6 +888,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123052756</v>
+        <v>123037348</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,37 +960,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493511</v>
+        <v>493257</v>
       </c>
       <c r="R4" t="n">
-        <v>7009902</v>
+        <v>7009814</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1038,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en undertryckt döende gran.</t>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1052,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1028,12 +1067,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1051,10 +1090,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123054425</v>
+        <v>123055634</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,21 +1106,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,13 +1130,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493457</v>
+        <v>493359</v>
       </c>
       <c r="R5" t="n">
-        <v>7009914</v>
+        <v>7009921</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,7 +1170,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,22 +1189,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1183,10 +1222,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123050424</v>
+        <v>123053948</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1223,13 +1262,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493465</v>
+        <v>493492</v>
       </c>
       <c r="R6" t="n">
-        <v>7009851</v>
+        <v>7009923</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,7 +1302,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,10 +1354,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123046087</v>
+        <v>123041637</v>
       </c>
       <c r="B7" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,46 +1366,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493418</v>
+        <v>493411</v>
       </c>
       <c r="R7" t="n">
-        <v>7009830</v>
+        <v>7009877</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,7 +1434,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en yngre mer smal sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,22 +1453,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1452,10 +1486,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123055634</v>
+        <v>123055266</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>100636</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1464,41 +1498,51 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493359</v>
+        <v>493376</v>
       </c>
       <c r="R8" t="n">
-        <v>7009921</v>
+        <v>7009926</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1530,11 +1574,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1547,26 +1586,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1584,10 +1603,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123052141</v>
+        <v>123046087</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>79881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1596,41 +1615,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493514</v>
+        <v>493418</v>
       </c>
       <c r="R9" t="n">
-        <v>7009883</v>
+        <v>7009830</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en yngre mer smal sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,22 +1707,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1719,7 +1743,7 @@
         <v>123052532</v>
       </c>
       <c r="B10" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1848,10 +1872,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123053948</v>
+        <v>123039688</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1864,37 +1888,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493492</v>
+        <v>493434</v>
       </c>
       <c r="R11" t="n">
-        <v>7009923</v>
+        <v>7009876</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1928,7 +1966,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1957,12 +1995,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1980,10 +2018,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123034670</v>
+        <v>123054425</v>
       </c>
       <c r="B12" t="n">
-        <v>57634</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1996,51 +2034,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493328</v>
+        <v>493457</v>
       </c>
       <c r="R12" t="n">
-        <v>7009783</v>
+        <v>7009914</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2074,7 +2098,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2089,6 +2113,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2106,10 +2150,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123037385</v>
+        <v>123047267</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>90975</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2122,36 +2166,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2160,13 +2195,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493280</v>
+        <v>493446</v>
       </c>
       <c r="R13" t="n">
-        <v>7009843</v>
+        <v>7009806</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2198,11 +2233,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2215,6 +2245,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2232,10 +2282,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123049755</v>
+        <v>123034670</v>
       </c>
       <c r="B14" t="n">
-        <v>78769</v>
+        <v>57634</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2248,37 +2298,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493474</v>
+        <v>493328</v>
       </c>
       <c r="R14" t="n">
-        <v>7009808</v>
+        <v>7009783</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2310,6 +2374,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2322,26 +2391,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2359,10 +2408,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123039744</v>
+        <v>123037385</v>
       </c>
       <c r="B15" t="n">
-        <v>78769</v>
+        <v>57634</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2375,37 +2424,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493408</v>
+        <v>493280</v>
       </c>
       <c r="R15" t="n">
-        <v>7009898</v>
+        <v>7009843</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2437,6 +2500,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2449,26 +2517,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2486,10 +2534,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123047649</v>
+        <v>123052756</v>
       </c>
       <c r="B16" t="n">
-        <v>90973</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2502,42 +2550,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493432</v>
+        <v>493511</v>
       </c>
       <c r="R16" t="n">
-        <v>7009795</v>
+        <v>7009902</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2571,7 +2614,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
+          <t>På en undertryckt döende gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2585,7 +2628,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2600,12 +2643,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,10 +2666,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123035251</v>
+        <v>123054162</v>
       </c>
       <c r="B17" t="n">
-        <v>57634</v>
+        <v>78771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2639,51 +2682,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493214</v>
+        <v>493462</v>
       </c>
       <c r="R17" t="n">
-        <v>7009801</v>
+        <v>7009883</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2717,7 +2746,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2731,7 +2760,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2752,7 +2801,7 @@
         <v>123041745</v>
       </c>
       <c r="B18" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2881,10 +2930,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123034217</v>
+        <v>123047649</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2897,34 +2946,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493321</v>
+        <v>493432</v>
       </c>
       <c r="R19" t="n">
-        <v>7009835</v>
+        <v>7009795</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2959,6 +3013,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Växer i en relativt grov stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2985,12 +3044,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3008,10 +3067,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123037348</v>
+        <v>123057555</v>
       </c>
       <c r="B20" t="n">
-        <v>90973</v>
+        <v>57634</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3024,36 +3083,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3062,13 +3121,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493257</v>
+        <v>493366</v>
       </c>
       <c r="R20" t="n">
-        <v>7009814</v>
+        <v>7009842</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3102,7 +3161,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3117,26 +3176,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3157,7 +3196,7 @@
         <v>123049318</v>
       </c>
       <c r="B21" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3286,10 +3325,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123039688</v>
+        <v>123035251</v>
       </c>
       <c r="B22" t="n">
-        <v>90973</v>
+        <v>57634</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3302,36 +3341,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3340,10 +3379,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493434</v>
+        <v>493214</v>
       </c>
       <c r="R22" t="n">
-        <v>7009876</v>
+        <v>7009801</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
@@ -3380,7 +3419,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3395,26 +3434,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3432,10 +3451,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123055266</v>
+        <v>123047895</v>
       </c>
       <c r="B23" t="n">
-        <v>100634</v>
+        <v>97324</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3448,21 +3467,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3471,24 +3490,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493376</v>
+        <v>493424</v>
       </c>
       <c r="R23" t="n">
-        <v>7009926</v>
+        <v>7009777</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3549,10 +3563,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123047267</v>
+        <v>123057570</v>
       </c>
       <c r="B24" t="n">
-        <v>90973</v>
+        <v>97324</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3561,31 +3575,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3594,13 +3608,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493446</v>
+        <v>493373</v>
       </c>
       <c r="R24" t="n">
-        <v>7009806</v>
+        <v>7009844</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3644,26 +3658,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3681,10 +3675,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123046193</v>
+        <v>123049755</v>
       </c>
       <c r="B25" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3721,13 +3715,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493415</v>
+        <v>493474</v>
       </c>
       <c r="R25" t="n">
-        <v>7009815</v>
+        <v>7009808</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3757,11 +3751,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3813,10 +3802,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123041637</v>
+        <v>123039744</v>
       </c>
       <c r="B26" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3853,13 +3842,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493411</v>
+        <v>493408</v>
       </c>
       <c r="R26" t="n">
-        <v>7009877</v>
+        <v>7009898</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3889,11 +3878,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3945,10 +3929,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123054162</v>
+        <v>123046193</v>
       </c>
       <c r="B27" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3985,13 +3969,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493462</v>
+        <v>493415</v>
       </c>
       <c r="R27" t="n">
-        <v>7009883</v>
+        <v>7009815</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4025,7 +4009,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4039,7 +4023,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4054,12 +4038,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4077,10 +4061,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123046343</v>
+        <v>123034217</v>
       </c>
       <c r="B28" t="n">
-        <v>90955</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4093,42 +4077,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493442</v>
+        <v>493321</v>
       </c>
       <c r="R28" t="n">
-        <v>7009799</v>
+        <v>7009835</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4160,11 +4139,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4191,12 +4165,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4214,10 +4188,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123047895</v>
+        <v>123050424</v>
       </c>
       <c r="B29" t="n">
-        <v>97322</v>
+        <v>78771</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4226,46 +4200,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493424</v>
+        <v>493465</v>
       </c>
       <c r="R29" t="n">
-        <v>7009777</v>
+        <v>7009851</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4297,6 +4266,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4309,6 +4283,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4326,10 +4320,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123057555</v>
+        <v>123048347</v>
       </c>
       <c r="B30" t="n">
-        <v>57634</v>
+        <v>90957</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4342,36 +4336,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4380,13 +4365,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493366</v>
+        <v>493416</v>
       </c>
       <c r="R30" t="n">
-        <v>7009842</v>
+        <v>7009768</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4418,11 +4403,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4435,6 +4415,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4455,7 +4455,7 @@
         <v>123135507</v>
       </c>
       <c r="B31" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>123056726</v>
       </c>
       <c r="B32" t="n">
-        <v>91648</v>
+        <v>91650</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123046343</v>
+        <v>123055634</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,39 +823,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493442</v>
+        <v>493359</v>
       </c>
       <c r="R3" t="n">
-        <v>7009799</v>
+        <v>7009921</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -892,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +906,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123037348</v>
+        <v>123046343</v>
       </c>
       <c r="B4" t="n">
-        <v>90975</v>
+        <v>90957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,33 +955,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -998,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493257</v>
+        <v>493442</v>
       </c>
       <c r="R4" t="n">
-        <v>7009814</v>
+        <v>7009799</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1038,7 +1024,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,12 +1053,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123055634</v>
+        <v>123037348</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>90975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,34 +1092,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493359</v>
+        <v>493257</v>
       </c>
       <c r="R5" t="n">
-        <v>7009921</v>
+        <v>7009814</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,22 +1189,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123055266</v>
+        <v>123046087</v>
       </c>
       <c r="B8" t="n">
-        <v>100636</v>
+        <v>79881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,32 +1502,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1536,13 +1531,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493376</v>
+        <v>493418</v>
       </c>
       <c r="R8" t="n">
-        <v>7009926</v>
+        <v>7009830</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1574,6 +1569,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en yngre mer smal sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1586,6 +1586,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1603,10 +1623,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123046087</v>
+        <v>123055266</v>
       </c>
       <c r="B9" t="n">
-        <v>79881</v>
+        <v>100636</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1619,27 +1639,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1648,13 +1673,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493418</v>
+        <v>493376</v>
       </c>
       <c r="R9" t="n">
-        <v>7009830</v>
+        <v>7009926</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1686,11 +1711,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På en yngre mer smal sälg.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1703,26 +1723,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123052141</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123055634</v>
+        <v>123041745</v>
       </c>
       <c r="B3" t="n">
-        <v>79852</v>
+        <v>90981</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,37 +823,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493359</v>
+        <v>493424</v>
       </c>
       <c r="R3" t="n">
-        <v>7009921</v>
+        <v>7009866</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +890,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -906,22 +906,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123046343</v>
+        <v>123054425</v>
       </c>
       <c r="B4" t="n">
-        <v>90957</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,42 +955,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493442</v>
+        <v>493457</v>
       </c>
       <c r="R4" t="n">
-        <v>7009799</v>
+        <v>7009914</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,12 +1048,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123037348</v>
+        <v>123049318</v>
       </c>
       <c r="B5" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,51 +1087,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493257</v>
+        <v>493450</v>
       </c>
       <c r="R5" t="n">
-        <v>7009814</v>
+        <v>7009784</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1170,7 +1151,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,12 +1180,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1222,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123053948</v>
+        <v>123034217</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1262,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493492</v>
+        <v>493321</v>
       </c>
       <c r="R6" t="n">
-        <v>7009923</v>
+        <v>7009835</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1298,11 +1279,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1354,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123041637</v>
+        <v>123039744</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1394,13 +1370,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493411</v>
+        <v>493408</v>
       </c>
       <c r="R7" t="n">
-        <v>7009877</v>
+        <v>7009898</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1430,11 +1406,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1486,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123046087</v>
+        <v>123034670</v>
       </c>
       <c r="B8" t="n">
-        <v>79881</v>
+        <v>57634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1498,31 +1469,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1531,13 +1511,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493418</v>
+        <v>493328</v>
       </c>
       <c r="R8" t="n">
-        <v>7009830</v>
+        <v>7009783</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1571,7 +1551,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en yngre mer smal sälg.</t>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,26 +1566,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1623,10 +1583,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123055266</v>
+        <v>123057555</v>
       </c>
       <c r="B9" t="n">
-        <v>100636</v>
+        <v>57634</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1635,31 +1595,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1673,13 +1637,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493376</v>
+        <v>493366</v>
       </c>
       <c r="R9" t="n">
-        <v>7009926</v>
+        <v>7009842</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1709,6 +1673,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1740,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123052532</v>
+        <v>123046193</v>
       </c>
       <c r="B10" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1756,42 +1725,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493540</v>
+        <v>493415</v>
       </c>
       <c r="R10" t="n">
-        <v>7009891</v>
+        <v>7009815</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1823,6 +1787,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1834,7 +1803,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1849,12 +1818,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1872,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123039688</v>
+        <v>123046087</v>
       </c>
       <c r="B11" t="n">
-        <v>90975</v>
+        <v>79882</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1884,40 +1853,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1926,13 +1886,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493434</v>
+        <v>493418</v>
       </c>
       <c r="R11" t="n">
-        <v>7009876</v>
+        <v>7009830</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1966,7 +1926,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>På en yngre mer smal sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1985,22 +1945,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2018,10 +1978,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123054425</v>
+        <v>123037385</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>57634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2034,34 +1994,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493457</v>
+        <v>493280</v>
       </c>
       <c r="R12" t="n">
-        <v>7009914</v>
+        <v>7009843</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2098,7 +2072,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,26 +2087,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2150,10 +2104,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123047267</v>
+        <v>123037348</v>
       </c>
       <c r="B13" t="n">
-        <v>90975</v>
+        <v>90981</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2183,7 +2137,16 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2195,13 +2158,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493446</v>
+        <v>493257</v>
       </c>
       <c r="R13" t="n">
-        <v>7009806</v>
+        <v>7009814</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2233,6 +2196,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2259,12 +2227,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2282,10 +2250,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123034670</v>
+        <v>123039688</v>
       </c>
       <c r="B14" t="n">
-        <v>57634</v>
+        <v>90981</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2298,21 +2266,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2320,14 +2288,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2336,13 +2304,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493328</v>
+        <v>493434</v>
       </c>
       <c r="R14" t="n">
-        <v>7009783</v>
+        <v>7009876</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2376,7 +2344,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2391,6 +2359,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2408,10 +2396,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123037385</v>
+        <v>123055634</v>
       </c>
       <c r="B15" t="n">
-        <v>57634</v>
+        <v>79853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2424,51 +2412,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493280</v>
+        <v>493359</v>
       </c>
       <c r="R15" t="n">
-        <v>7009843</v>
+        <v>7009921</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2502,7 +2476,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2517,6 +2491,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2534,10 +2528,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123052756</v>
+        <v>123035251</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>57634</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2550,37 +2544,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493511</v>
+        <v>493214</v>
       </c>
       <c r="R16" t="n">
-        <v>7009902</v>
+        <v>7009801</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2614,7 +2622,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en undertryckt döende gran.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2628,27 +2636,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2666,10 +2654,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123054162</v>
+        <v>123049755</v>
       </c>
       <c r="B17" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2706,13 +2694,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493462</v>
+        <v>493474</v>
       </c>
       <c r="R17" t="n">
-        <v>7009883</v>
+        <v>7009808</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2744,11 +2732,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2760,7 +2743,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2775,12 +2758,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2798,10 +2781,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123041745</v>
+        <v>123041637</v>
       </c>
       <c r="B18" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2814,42 +2797,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493424</v>
+        <v>493411</v>
       </c>
       <c r="R18" t="n">
-        <v>7009866</v>
+        <v>7009877</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2881,6 +2859,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2907,12 +2890,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2930,10 +2913,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123047649</v>
+        <v>123047895</v>
       </c>
       <c r="B19" t="n">
-        <v>90975</v>
+        <v>97330</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2942,31 +2925,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2975,13 +2958,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493432</v>
+        <v>493424</v>
       </c>
       <c r="R19" t="n">
-        <v>7009795</v>
+        <v>7009777</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3013,11 +2996,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3030,26 +3008,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3067,10 +3025,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123057555</v>
+        <v>123048347</v>
       </c>
       <c r="B20" t="n">
-        <v>57634</v>
+        <v>90963</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3083,36 +3041,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3121,13 +3070,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493366</v>
+        <v>493416</v>
       </c>
       <c r="R20" t="n">
-        <v>7009842</v>
+        <v>7009768</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3159,11 +3108,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3176,6 +3120,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3193,10 +3157,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123049318</v>
+        <v>123057570</v>
       </c>
       <c r="B21" t="n">
-        <v>78771</v>
+        <v>97330</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3205,38 +3169,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493450</v>
+        <v>493373</v>
       </c>
       <c r="R21" t="n">
-        <v>7009784</v>
+        <v>7009844</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3271,11 +3240,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3288,26 +3252,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3325,10 +3269,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123035251</v>
+        <v>123052532</v>
       </c>
       <c r="B22" t="n">
-        <v>57634</v>
+        <v>90981</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3341,36 +3285,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3379,13 +3314,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493214</v>
+        <v>493540</v>
       </c>
       <c r="R22" t="n">
-        <v>7009801</v>
+        <v>7009891</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3417,11 +3352,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3433,7 +3363,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3451,10 +3401,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123047895</v>
+        <v>123052756</v>
       </c>
       <c r="B23" t="n">
-        <v>97324</v>
+        <v>78772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3463,43 +3413,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493424</v>
+        <v>493511</v>
       </c>
       <c r="R23" t="n">
-        <v>7009777</v>
+        <v>7009902</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3534,6 +3479,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en undertryckt döende gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3545,7 +3495,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3563,10 +3533,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123057570</v>
+        <v>123054162</v>
       </c>
       <c r="B24" t="n">
-        <v>97324</v>
+        <v>78772</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3575,46 +3545,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493373</v>
+        <v>493462</v>
       </c>
       <c r="R24" t="n">
-        <v>7009844</v>
+        <v>7009883</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3646,6 +3611,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3657,7 +3627,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3675,10 +3665,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123049755</v>
+        <v>123047267</v>
       </c>
       <c r="B25" t="n">
-        <v>78771</v>
+        <v>90981</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3691,34 +3681,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493474</v>
+        <v>493446</v>
       </c>
       <c r="R25" t="n">
-        <v>7009808</v>
+        <v>7009806</v>
       </c>
       <c r="S25" t="n">
         <v>12</v>
@@ -3779,12 +3774,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3802,10 +3797,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123039744</v>
+        <v>123047649</v>
       </c>
       <c r="B26" t="n">
-        <v>78771</v>
+        <v>90981</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3818,37 +3813,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493408</v>
+        <v>493432</v>
       </c>
       <c r="R26" t="n">
-        <v>7009898</v>
+        <v>7009795</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3880,6 +3880,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer i en relativt grov stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3906,12 +3911,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3929,10 +3934,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123046193</v>
+        <v>123046343</v>
       </c>
       <c r="B27" t="n">
-        <v>78771</v>
+        <v>90963</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3945,37 +3950,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493415</v>
+        <v>493442</v>
       </c>
       <c r="R27" t="n">
-        <v>7009815</v>
+        <v>7009799</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4009,7 +4019,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4038,12 +4048,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4061,10 +4071,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123034217</v>
+        <v>123053948</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4101,10 +4111,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493321</v>
+        <v>493492</v>
       </c>
       <c r="R28" t="n">
-        <v>7009835</v>
+        <v>7009923</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
@@ -4137,6 +4147,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4191,7 +4206,7 @@
         <v>123050424</v>
       </c>
       <c r="B29" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4320,10 +4335,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123048347</v>
+        <v>123055266</v>
       </c>
       <c r="B30" t="n">
-        <v>90957</v>
+        <v>100642</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4332,31 +4347,36 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4365,13 +4385,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493416</v>
+        <v>493376</v>
       </c>
       <c r="R30" t="n">
-        <v>7009768</v>
+        <v>7009926</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4415,26 +4435,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123135507</v>
+        <v>123056726</v>
       </c>
       <c r="B31" t="n">
-        <v>90957</v>
+        <v>91656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4464,25 +4464,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4505,7 +4505,7 @@
         <v>7009914</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4535,6 +4535,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4564,12 +4569,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4587,10 +4592,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123056726</v>
+        <v>123135507</v>
       </c>
       <c r="B32" t="n">
-        <v>91650</v>
+        <v>90963</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4599,25 +4604,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4630,7 +4635,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynjelägden, Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4640,7 +4645,7 @@
         <v>7009914</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4670,11 +4675,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -1857,10 +1857,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123046087</v>
+        <v>123034217</v>
       </c>
       <c r="B11" t="n">
-        <v>79885</v>
+        <v>78775</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1869,46 +1869,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493418</v>
+        <v>493321</v>
       </c>
       <c r="R11" t="n">
-        <v>7009830</v>
+        <v>7009835</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1940,11 +1935,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en yngre mer smal sälg.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1961,22 +1951,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1994,10 +1984,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123034217</v>
+        <v>123046087</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>79885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2006,41 +1996,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493321</v>
+        <v>493418</v>
       </c>
       <c r="R12" t="n">
-        <v>7009835</v>
+        <v>7009830</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2072,6 +2067,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en yngre mer smal sälg.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2088,22 +2088,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123048347</v>
+        <v>123052756</v>
       </c>
       <c r="B17" t="n">
-        <v>90966</v>
+        <v>78775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2668,42 +2668,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493416</v>
+        <v>493511</v>
       </c>
       <c r="R17" t="n">
-        <v>7009768</v>
+        <v>7009902</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2735,6 +2730,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en undertryckt döende gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2761,12 +2761,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123052756</v>
+        <v>123048347</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>90966</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2800,37 +2800,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493511</v>
+        <v>493416</v>
       </c>
       <c r="R18" t="n">
-        <v>7009902</v>
+        <v>7009768</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2862,11 +2867,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en undertryckt döende gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123041637</v>
+        <v>123046343</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493411</v>
+        <v>493442</v>
       </c>
       <c r="R2" t="n">
-        <v>7009877</v>
+        <v>7009799</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -755,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +789,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,7 +815,7 @@
         <v>123046193</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -939,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123049755</v>
+        <v>123057570</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>97350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,41 +956,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493474</v>
+        <v>493373</v>
       </c>
       <c r="R4" t="n">
-        <v>7009808</v>
+        <v>7009844</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,26 +1039,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123049318</v>
+        <v>123054162</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,13 +1096,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493450</v>
+        <v>493462</v>
       </c>
       <c r="R5" t="n">
-        <v>7009784</v>
+        <v>7009883</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1136,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,7 +1150,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1175,12 +1165,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123035251</v>
+        <v>123041745</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>91001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1214,36 +1204,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1252,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493214</v>
+        <v>493424</v>
       </c>
       <c r="R6" t="n">
-        <v>7009801</v>
+        <v>7009866</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
@@ -1290,11 +1271,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1307,6 +1283,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1324,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123050424</v>
+        <v>123041637</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1364,10 +1360,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493465</v>
+        <v>493411</v>
       </c>
       <c r="R7" t="n">
-        <v>7009851</v>
+        <v>7009877</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1456,10 +1452,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123047649</v>
+        <v>123035251</v>
       </c>
       <c r="B8" t="n">
-        <v>90984</v>
+        <v>57640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,27 +1468,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1501,13 +1506,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493432</v>
+        <v>493214</v>
       </c>
       <c r="R8" t="n">
-        <v>7009795</v>
+        <v>7009801</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1541,7 +1546,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,26 +1561,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,10 +1578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123047267</v>
+        <v>123052532</v>
       </c>
       <c r="B9" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1638,13 +1623,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493446</v>
+        <v>493540</v>
       </c>
       <c r="R9" t="n">
-        <v>7009806</v>
+        <v>7009891</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1687,7 +1672,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1702,12 +1687,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1725,10 +1710,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123041745</v>
+        <v>123048347</v>
       </c>
       <c r="B10" t="n">
-        <v>90984</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1741,21 +1726,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1770,13 +1755,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493424</v>
+        <v>493416</v>
       </c>
       <c r="R10" t="n">
-        <v>7009866</v>
+        <v>7009768</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1834,12 +1819,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1857,10 +1842,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123034217</v>
+        <v>123039744</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1897,13 +1882,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493321</v>
+        <v>493408</v>
       </c>
       <c r="R11" t="n">
-        <v>7009835</v>
+        <v>7009898</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1984,10 +1969,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123046087</v>
+        <v>123053948</v>
       </c>
       <c r="B12" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1996,46 +1981,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493418</v>
+        <v>493492</v>
       </c>
       <c r="R12" t="n">
-        <v>7009830</v>
+        <v>7009923</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2069,7 +2049,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en yngre mer smal sälg.</t>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2088,22 +2068,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2121,10 +2101,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123034670</v>
+        <v>123049755</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2137,51 +2117,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493328</v>
+        <v>493474</v>
       </c>
       <c r="R13" t="n">
-        <v>7009783</v>
+        <v>7009808</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2213,11 +2179,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2230,6 +2191,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2247,10 +2228,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123039744</v>
+        <v>123046087</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2259,38 +2240,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493408</v>
+        <v>493418</v>
       </c>
       <c r="R14" t="n">
-        <v>7009898</v>
+        <v>7009830</v>
       </c>
       <c r="S14" t="n">
         <v>11</v>
@@ -2325,6 +2311,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en yngre mer smal sälg.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2341,22 +2332,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2374,10 +2365,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123053948</v>
+        <v>123037385</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>57640</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2390,37 +2381,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493492</v>
+        <v>493280</v>
       </c>
       <c r="R15" t="n">
-        <v>7009923</v>
+        <v>7009843</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2454,7 +2459,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2469,26 +2474,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2506,10 +2491,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123037348</v>
+        <v>123039688</v>
       </c>
       <c r="B16" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2541,7 +2526,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2560,13 +2545,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493257</v>
+        <v>493434</v>
       </c>
       <c r="R16" t="n">
-        <v>7009814</v>
+        <v>7009876</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2600,7 +2585,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2652,10 +2637,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123052756</v>
+        <v>123055266</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>100662</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2664,41 +2649,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493511</v>
+        <v>493376</v>
       </c>
       <c r="R17" t="n">
-        <v>7009902</v>
+        <v>7009926</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2730,11 +2725,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en undertryckt döende gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2746,27 +2736,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2784,10 +2754,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123048347</v>
+        <v>123037348</v>
       </c>
       <c r="B18" t="n">
-        <v>90966</v>
+        <v>91001</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2800,24 +2770,33 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2829,10 +2808,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493416</v>
+        <v>493257</v>
       </c>
       <c r="R18" t="n">
-        <v>7009768</v>
+        <v>7009814</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2867,6 +2846,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2893,12 +2877,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2919,7 +2903,7 @@
         <v>123057555</v>
       </c>
       <c r="B19" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3042,10 +3026,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123047895</v>
+        <v>123034217</v>
       </c>
       <c r="B20" t="n">
-        <v>97333</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3054,46 +3038,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493424</v>
+        <v>493321</v>
       </c>
       <c r="R20" t="n">
-        <v>7009777</v>
+        <v>7009835</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3137,6 +3116,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3154,10 +3153,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123037385</v>
+        <v>123055634</v>
       </c>
       <c r="B21" t="n">
-        <v>57634</v>
+        <v>79862</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3170,51 +3169,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493280</v>
+        <v>493359</v>
       </c>
       <c r="R21" t="n">
-        <v>7009843</v>
+        <v>7009921</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3248,7 +3233,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Enstaka bålar på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3263,6 +3248,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3280,10 +3285,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123054162</v>
+        <v>123047895</v>
       </c>
       <c r="B22" t="n">
-        <v>78775</v>
+        <v>97350</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3292,41 +3297,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493462</v>
+        <v>493424</v>
       </c>
       <c r="R22" t="n">
-        <v>7009883</v>
+        <v>7009777</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3358,11 +3368,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3374,27 +3379,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3412,10 +3397,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123052141</v>
+        <v>123054425</v>
       </c>
       <c r="B23" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3452,13 +3437,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493514</v>
+        <v>493457</v>
       </c>
       <c r="R23" t="n">
-        <v>7009883</v>
+        <v>7009914</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3521,12 +3506,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3544,10 +3529,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123057570</v>
+        <v>123034670</v>
       </c>
       <c r="B24" t="n">
-        <v>97333</v>
+        <v>57640</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3556,31 +3541,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3589,13 +3583,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493373</v>
+        <v>493328</v>
       </c>
       <c r="R24" t="n">
-        <v>7009844</v>
+        <v>7009783</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3625,6 +3619,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3656,10 +3655,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123046343</v>
+        <v>123047649</v>
       </c>
       <c r="B25" t="n">
-        <v>90966</v>
+        <v>91001</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3672,21 +3671,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3701,13 +3700,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493442</v>
+        <v>493432</v>
       </c>
       <c r="R25" t="n">
-        <v>7009799</v>
+        <v>7009795</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3741,7 +3740,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Växer i en relativt grov stående döende gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3770,12 +3769,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3793,10 +3792,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123055266</v>
+        <v>123047267</v>
       </c>
       <c r="B26" t="n">
-        <v>100645</v>
+        <v>91001</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3805,36 +3804,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3843,13 +3837,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493376</v>
+        <v>493446</v>
       </c>
       <c r="R26" t="n">
-        <v>7009926</v>
+        <v>7009806</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3893,6 +3887,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3910,10 +3924,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123039688</v>
+        <v>123052141</v>
       </c>
       <c r="B27" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3926,51 +3940,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493434</v>
+        <v>493514</v>
       </c>
       <c r="R27" t="n">
-        <v>7009876</v>
+        <v>7009883</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4056,10 +4056,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123054425</v>
+        <v>123050424</v>
       </c>
       <c r="B28" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4096,13 +4096,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493457</v>
+        <v>493465</v>
       </c>
       <c r="R28" t="n">
-        <v>7009914</v>
+        <v>7009851</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123055634</v>
+        <v>123052756</v>
       </c>
       <c r="B29" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4228,13 +4228,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493359</v>
+        <v>493511</v>
       </c>
       <c r="R29" t="n">
-        <v>7009921</v>
+        <v>7009902</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en flerstammig sälg.</t>
+          <t>På en undertryckt döende gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4282,27 +4282,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123052532</v>
+        <v>123049318</v>
       </c>
       <c r="B30" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4336,42 +4336,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493540</v>
+        <v>493450</v>
       </c>
       <c r="R30" t="n">
-        <v>7009891</v>
+        <v>7009784</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4403,6 +4398,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123135507</v>
+        <v>123056726</v>
       </c>
       <c r="B31" t="n">
-        <v>90966</v>
+        <v>91676</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4464,25 +4464,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4505,7 +4505,7 @@
         <v>7009914</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4535,6 +4535,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4564,12 +4569,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4587,10 +4592,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123056726</v>
+        <v>123135507</v>
       </c>
       <c r="B32" t="n">
-        <v>91659</v>
+        <v>90983</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4599,25 +4604,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4630,7 +4635,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynjelägden, Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4640,7 +4645,7 @@
         <v>7009914</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4670,11 +4675,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123619506</v>
+        <v>123617329</v>
       </c>
       <c r="B33" t="n">
-        <v>98379</v>
+        <v>57857</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4739,31 +4739,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4777,13 +4786,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493457</v>
+        <v>493431</v>
       </c>
       <c r="R33" t="n">
-        <v>7009777</v>
+        <v>7009773</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4817,7 +4826,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4849,10 +4858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617140</v>
+        <v>123616525</v>
       </c>
       <c r="B34" t="n">
-        <v>57851</v>
+        <v>100662</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4865,41 +4874,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4908,13 +4903,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493469</v>
+        <v>493367</v>
       </c>
       <c r="R34" t="n">
-        <v>7009816</v>
+        <v>7009852</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4944,11 +4939,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4980,10 +4970,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123616867</v>
+        <v>123616609</v>
       </c>
       <c r="B35" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5025,13 +5015,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493384</v>
+        <v>493390</v>
       </c>
       <c r="R35" t="n">
-        <v>7009812</v>
+        <v>7009845</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5092,10 +5082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617207</v>
+        <v>123617140</v>
       </c>
       <c r="B36" t="n">
-        <v>97333</v>
+        <v>57857</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5108,27 +5098,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5137,13 +5141,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493466</v>
+        <v>493469</v>
       </c>
       <c r="R36" t="n">
-        <v>7009777</v>
+        <v>7009816</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5173,6 +5177,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5204,10 +5213,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617329</v>
+        <v>123616867</v>
       </c>
       <c r="B37" t="n">
-        <v>57851</v>
+        <v>100662</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5220,41 +5229,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5263,13 +5258,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493431</v>
+        <v>493384</v>
       </c>
       <c r="R37" t="n">
-        <v>7009773</v>
+        <v>7009812</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5299,11 +5294,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5335,10 +5325,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123618504</v>
+        <v>123617207</v>
       </c>
       <c r="B38" t="n">
-        <v>98379</v>
+        <v>97350</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5347,60 +5337,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493449</v>
+        <v>493466</v>
       </c>
       <c r="R38" t="n">
-        <v>7009750</v>
+        <v>7009777</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5430,11 +5406,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5466,10 +5437,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123616525</v>
+        <v>123725484</v>
       </c>
       <c r="B39" t="n">
-        <v>100645</v>
+        <v>57857</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5482,27 +5453,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5511,13 +5496,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493367</v>
+        <v>493356</v>
       </c>
       <c r="R39" t="n">
-        <v>7009852</v>
+        <v>7009680</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5541,12 +5526,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5578,10 +5563,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123616609</v>
+        <v>123726570</v>
       </c>
       <c r="B40" t="n">
-        <v>100645</v>
+        <v>57640</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5590,31 +5575,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5623,13 +5617,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493390</v>
+        <v>493381</v>
       </c>
       <c r="R40" t="n">
-        <v>7009845</v>
+        <v>7009679</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5653,12 +5647,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5687,6 +5686,2645 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123733427</v>
+      </c>
+      <c r="B41" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>493324</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7009783</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123732386</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>493374</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7009884</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123733352</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>493302</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7009788</v>
+      </c>
+      <c r="S43" t="n">
+        <v>11</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123727458</v>
+      </c>
+      <c r="B44" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>493403</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7009782</v>
+      </c>
+      <c r="S44" t="n">
+        <v>11</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123725306</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97350</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>493390</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7009685</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123727294</v>
+      </c>
+      <c r="B46" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>493367</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7009725</v>
+      </c>
+      <c r="S46" t="n">
+        <v>14</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123733095</v>
+      </c>
+      <c r="B47" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>493278</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7009820</v>
+      </c>
+      <c r="S47" t="n">
+        <v>7</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123732971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>493336</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7009883</v>
+      </c>
+      <c r="S48" t="n">
+        <v>9</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123725818</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97350</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>493368</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7009687</v>
+      </c>
+      <c r="S49" t="n">
+        <v>8</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123733066</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97350</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>493280</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7009832</v>
+      </c>
+      <c r="S50" t="n">
+        <v>8</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123725949</v>
+      </c>
+      <c r="B51" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>493389</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7009683</v>
+      </c>
+      <c r="S51" t="n">
+        <v>8</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123730921</v>
+      </c>
+      <c r="B52" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>493438</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7009868</v>
+      </c>
+      <c r="S52" t="n">
+        <v>11</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123733311</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97350</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>493300</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7009795</v>
+      </c>
+      <c r="S53" t="n">
+        <v>9</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123726856</v>
+      </c>
+      <c r="B54" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>493371</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7009706</v>
+      </c>
+      <c r="S54" t="n">
+        <v>9</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>123726337</v>
+      </c>
+      <c r="B55" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>493412</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7009647</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>123730590</v>
+      </c>
+      <c r="B56" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>493530</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7009886</v>
+      </c>
+      <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>123618504</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>493449</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7009750</v>
+      </c>
+      <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>123619506</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>493457</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7009777</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>123730088</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>493472</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7009838</v>
+      </c>
+      <c r="S59" t="n">
+        <v>9</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>123728604</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>493379</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7009848</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>123725700</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>493341</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7009682</v>
+      </c>
+      <c r="S61" t="n">
+        <v>9</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123732177</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>493430</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7009898</v>
+      </c>
+      <c r="S62" t="n">
+        <v>9</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123046343</v>
+        <v>123046193</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493442</v>
+        <v>493415</v>
       </c>
       <c r="R2" t="n">
-        <v>7009799</v>
+        <v>7009815</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123046193</v>
+        <v>123046343</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +823,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493415</v>
+        <v>493442</v>
       </c>
       <c r="R3" t="n">
-        <v>7009815</v>
+        <v>7009799</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123034670</v>
+        <v>123047649</v>
       </c>
       <c r="B24" t="n">
-        <v>57640</v>
+        <v>91001</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3545,36 +3545,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3583,10 +3574,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493328</v>
+        <v>493432</v>
       </c>
       <c r="R24" t="n">
-        <v>7009783</v>
+        <v>7009795</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3623,7 +3614,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+          <t>Växer i en relativt grov stående döende gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3638,6 +3629,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3655,7 +3666,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123047649</v>
+        <v>123047267</v>
       </c>
       <c r="B25" t="n">
         <v>91001</v>
@@ -3700,13 +3711,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493432</v>
+        <v>493446</v>
       </c>
       <c r="R25" t="n">
-        <v>7009795</v>
+        <v>7009806</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3738,11 +3749,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3769,12 +3775,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3792,10 +3798,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123047267</v>
+        <v>123034670</v>
       </c>
       <c r="B26" t="n">
-        <v>91001</v>
+        <v>57640</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3808,27 +3814,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3837,13 +3852,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493446</v>
+        <v>493328</v>
       </c>
       <c r="R26" t="n">
-        <v>7009806</v>
+        <v>7009783</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3875,6 +3890,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3887,26 +3907,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -6269,7 +6269,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123727294</v>
+        <v>123733095</v>
       </c>
       <c r="B46" t="n">
         <v>100662</v>
@@ -6319,13 +6319,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493367</v>
+        <v>493278</v>
       </c>
       <c r="R46" t="n">
-        <v>7009725</v>
+        <v>7009820</v>
       </c>
       <c r="S46" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123733095</v>
+        <v>123727294</v>
       </c>
       <c r="B47" t="n">
         <v>100662</v>
@@ -6436,13 +6436,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493278</v>
+        <v>493367</v>
       </c>
       <c r="R47" t="n">
-        <v>7009820</v>
+        <v>7009725</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123046193</v>
+        <v>123046343</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493415</v>
+        <v>493442</v>
       </c>
       <c r="R2" t="n">
-        <v>7009815</v>
+        <v>7009799</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +789,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123046343</v>
+        <v>123046193</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493442</v>
+        <v>493415</v>
       </c>
       <c r="R3" t="n">
-        <v>7009799</v>
+        <v>7009815</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123041637</v>
+        <v>123052532</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>91001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,34 +1336,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493411</v>
+        <v>493540</v>
       </c>
       <c r="R7" t="n">
-        <v>7009877</v>
+        <v>7009891</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1398,11 +1403,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123035251</v>
+        <v>123041637</v>
       </c>
       <c r="B8" t="n">
-        <v>57640</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1468,51 +1468,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493214</v>
+        <v>493411</v>
       </c>
       <c r="R8" t="n">
-        <v>7009801</v>
+        <v>7009877</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1546,7 +1532,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1561,6 +1547,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1578,10 +1584,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123052532</v>
+        <v>123035251</v>
       </c>
       <c r="B9" t="n">
-        <v>91001</v>
+        <v>57640</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1594,27 +1600,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1623,13 +1638,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493540</v>
+        <v>493214</v>
       </c>
       <c r="R9" t="n">
-        <v>7009891</v>
+        <v>7009801</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1661,6 +1676,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1672,27 +1692,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123037348</v>
+        <v>123057555</v>
       </c>
       <c r="B18" t="n">
-        <v>91001</v>
+        <v>57640</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2770,36 +2770,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493257</v>
+        <v>493366</v>
       </c>
       <c r="R18" t="n">
-        <v>7009814</v>
+        <v>7009842</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2863,26 +2863,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2900,10 +2880,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123057555</v>
+        <v>123037348</v>
       </c>
       <c r="B19" t="n">
-        <v>57640</v>
+        <v>91001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2916,36 +2896,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2954,13 +2934,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493366</v>
+        <v>493257</v>
       </c>
       <c r="R19" t="n">
-        <v>7009842</v>
+        <v>7009814</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2994,7 +2974,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3009,6 +2989,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123046343</v>
+        <v>123046193</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493442</v>
+        <v>493415</v>
       </c>
       <c r="R2" t="n">
-        <v>7009799</v>
+        <v>7009815</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123046193</v>
+        <v>123046343</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +823,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493415</v>
+        <v>493442</v>
       </c>
       <c r="R3" t="n">
-        <v>7009815</v>
+        <v>7009799</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +921,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123057555</v>
+        <v>123037348</v>
       </c>
       <c r="B18" t="n">
-        <v>57640</v>
+        <v>91001</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2770,36 +2770,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493366</v>
+        <v>493257</v>
       </c>
       <c r="R18" t="n">
-        <v>7009842</v>
+        <v>7009814</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2863,6 +2863,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2880,10 +2900,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123037348</v>
+        <v>123057555</v>
       </c>
       <c r="B19" t="n">
-        <v>91001</v>
+        <v>57640</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2896,36 +2916,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2934,13 +2954,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493257</v>
+        <v>493366</v>
       </c>
       <c r="R19" t="n">
-        <v>7009814</v>
+        <v>7009842</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2974,7 +2994,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2989,26 +3009,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123047895</v>
+        <v>123054425</v>
       </c>
       <c r="B22" t="n">
-        <v>97350</v>
+        <v>78781</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3297,43 +3297,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493424</v>
+        <v>493457</v>
       </c>
       <c r="R22" t="n">
-        <v>7009777</v>
+        <v>7009914</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3368,6 +3363,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3380,6 +3380,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3397,10 +3417,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123054425</v>
+        <v>123047895</v>
       </c>
       <c r="B23" t="n">
-        <v>78781</v>
+        <v>97350</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3409,38 +3429,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493457</v>
+        <v>493424</v>
       </c>
       <c r="R23" t="n">
-        <v>7009914</v>
+        <v>7009777</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3475,11 +3500,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3492,26 +3512,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123730921</v>
+        <v>123733311</v>
       </c>
       <c r="B52" t="n">
-        <v>100662</v>
+        <v>97350</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6987,21 +6987,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7010,24 +7010,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493438</v>
+        <v>493300</v>
       </c>
       <c r="R52" t="n">
-        <v>7009868</v>
+        <v>7009795</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7070,7 +7065,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7088,10 +7083,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123733311</v>
+        <v>123730921</v>
       </c>
       <c r="B53" t="n">
-        <v>97350</v>
+        <v>100662</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7104,21 +7099,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7127,19 +7122,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493300</v>
+        <v>493438</v>
       </c>
       <c r="R53" t="n">
-        <v>7009795</v>
+        <v>7009868</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123046193</v>
+        <v>123054425</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493415</v>
+        <v>493457</v>
       </c>
       <c r="R2" t="n">
-        <v>7009815</v>
+        <v>7009914</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123046343</v>
+        <v>123041637</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,39 +823,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493442</v>
+        <v>493411</v>
       </c>
       <c r="R3" t="n">
-        <v>7009799</v>
+        <v>7009877</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -892,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I gammal granskog med bitvis goda mängder död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +916,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123057570</v>
+        <v>123053948</v>
       </c>
       <c r="B4" t="n">
-        <v>97350</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,46 +951,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493373</v>
+        <v>493492</v>
       </c>
       <c r="R4" t="n">
-        <v>7009844</v>
+        <v>7009923</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,6 +1017,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,6 +1034,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123054162</v>
+        <v>123037348</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>91006</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,37 +1087,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493462</v>
+        <v>493257</v>
       </c>
       <c r="R5" t="n">
-        <v>7009883</v>
+        <v>7009814</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,7 +1165,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1179,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1188,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041745</v>
+        <v>123057570</v>
       </c>
       <c r="B6" t="n">
-        <v>91001</v>
+        <v>97367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,31 +1229,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1233,13 +1262,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493424</v>
+        <v>493373</v>
       </c>
       <c r="R6" t="n">
-        <v>7009866</v>
+        <v>7009844</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1283,26 +1312,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123052532</v>
+        <v>123055266</v>
       </c>
       <c r="B7" t="n">
-        <v>91001</v>
+        <v>100680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,31 +1341,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1365,13 +1379,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493540</v>
+        <v>493376</v>
       </c>
       <c r="R7" t="n">
-        <v>7009891</v>
+        <v>7009926</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1414,27 +1428,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1452,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123041637</v>
+        <v>123052141</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1492,13 +1486,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493411</v>
+        <v>493514</v>
       </c>
       <c r="R8" t="n">
-        <v>7009877</v>
+        <v>7009883</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1561,12 +1555,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1584,10 +1578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123035251</v>
+        <v>123047895</v>
       </c>
       <c r="B9" t="n">
-        <v>57640</v>
+        <v>97367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1596,40 +1590,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1638,13 +1623,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493214</v>
+        <v>493424</v>
       </c>
       <c r="R9" t="n">
-        <v>7009801</v>
+        <v>7009777</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1674,11 +1659,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,10 +1690,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123048347</v>
+        <v>123046087</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>79896</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1722,31 +1702,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1755,13 +1735,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493416</v>
+        <v>493418</v>
       </c>
       <c r="R10" t="n">
-        <v>7009768</v>
+        <v>7009830</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1793,6 +1773,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en yngre mer smal sälg.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1809,22 +1794,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1842,10 +1827,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123039744</v>
+        <v>123037385</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>57643</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1858,37 +1843,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493408</v>
+        <v>493280</v>
       </c>
       <c r="R11" t="n">
-        <v>7009898</v>
+        <v>7009843</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1920,6 +1919,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1932,26 +1936,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1969,10 +1953,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123053948</v>
+        <v>123041745</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>91006</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,37 +1969,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493492</v>
+        <v>493424</v>
       </c>
       <c r="R12" t="n">
-        <v>7009923</v>
+        <v>7009866</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,11 +2036,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på nedre torra döda grenar på en gran med ca 45 cm i brösthöjdsdiameter i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2078,12 +2062,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2101,10 +2085,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123049755</v>
+        <v>123050424</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2141,13 +2125,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493474</v>
+        <v>493465</v>
       </c>
       <c r="R13" t="n">
-        <v>7009808</v>
+        <v>7009851</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2177,6 +2161,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2228,10 +2217,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123046087</v>
+        <v>123057555</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57643</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2240,31 +2229,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2273,13 +2271,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493418</v>
+        <v>493366</v>
       </c>
       <c r="R14" t="n">
-        <v>7009830</v>
+        <v>7009842</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2313,7 +2311,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På en yngre mer smal sälg.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,26 +2326,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2365,10 +2343,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123037385</v>
+        <v>123048347</v>
       </c>
       <c r="B15" t="n">
-        <v>57640</v>
+        <v>90988</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2381,36 +2359,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2419,13 +2388,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493280</v>
+        <v>493416</v>
       </c>
       <c r="R15" t="n">
-        <v>7009843</v>
+        <v>7009768</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2457,11 +2426,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2474,6 +2438,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2491,10 +2475,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123039688</v>
+        <v>123047267</v>
       </c>
       <c r="B16" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2524,16 +2508,7 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2545,13 +2520,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493434</v>
+        <v>493446</v>
       </c>
       <c r="R16" t="n">
-        <v>7009876</v>
+        <v>7009806</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2583,11 +2558,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2614,12 +2584,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2637,10 +2607,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123055266</v>
+        <v>123047649</v>
       </c>
       <c r="B17" t="n">
-        <v>100662</v>
+        <v>91006</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2649,36 +2619,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2687,10 +2652,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493376</v>
+        <v>493432</v>
       </c>
       <c r="R17" t="n">
-        <v>7009926</v>
+        <v>7009795</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2725,6 +2690,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Växer i en relativt grov stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2737,6 +2707,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2754,10 +2744,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123037348</v>
+        <v>123039744</v>
       </c>
       <c r="B18" t="n">
-        <v>91001</v>
+        <v>78786</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2770,51 +2760,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493257</v>
+        <v>493408</v>
       </c>
       <c r="R18" t="n">
-        <v>7009814</v>
+        <v>7009898</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2846,11 +2822,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2877,12 +2848,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2900,10 +2871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123057555</v>
+        <v>123046343</v>
       </c>
       <c r="B19" t="n">
-        <v>57640</v>
+        <v>90988</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2916,36 +2887,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2954,13 +2916,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493366</v>
+        <v>493442</v>
       </c>
       <c r="R19" t="n">
-        <v>7009842</v>
+        <v>7009799</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2994,7 +2956,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>I gammal granskog med bitvis goda mängder död ved.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3009,6 +2971,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3029,7 +3011,7 @@
         <v>123034217</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3156,7 +3138,7 @@
         <v>123055634</v>
       </c>
       <c r="B21" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3285,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123054425</v>
+        <v>123049318</v>
       </c>
       <c r="B22" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3325,10 +3307,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493457</v>
+        <v>493450</v>
       </c>
       <c r="R22" t="n">
-        <v>7009914</v>
+        <v>7009784</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3417,10 +3399,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123047895</v>
+        <v>123054162</v>
       </c>
       <c r="B23" t="n">
-        <v>97350</v>
+        <v>78786</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3429,46 +3411,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493424</v>
+        <v>493462</v>
       </c>
       <c r="R23" t="n">
-        <v>7009777</v>
+        <v>7009883</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3500,6 +3477,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3511,7 +3493,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3529,10 +3531,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123047649</v>
+        <v>123052532</v>
       </c>
       <c r="B24" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3574,13 +3576,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493432</v>
+        <v>493540</v>
       </c>
       <c r="R24" t="n">
-        <v>7009795</v>
+        <v>7009891</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3612,11 +3614,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växer i en relativt grov stående döende gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3628,7 +3625,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3643,12 +3640,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3666,10 +3663,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123047267</v>
+        <v>123039688</v>
       </c>
       <c r="B25" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3699,7 +3696,16 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3711,13 +3717,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493446</v>
+        <v>493434</v>
       </c>
       <c r="R25" t="n">
-        <v>7009806</v>
+        <v>7009876</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3749,6 +3755,11 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I stående död gran i gammal granskog med hyfsat gott om stående död ved.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3775,12 +3786,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3798,10 +3809,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123034670</v>
+        <v>123035251</v>
       </c>
       <c r="B26" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3833,7 +3844,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3852,13 +3863,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493328</v>
+        <v>493214</v>
       </c>
       <c r="R26" t="n">
-        <v>7009783</v>
+        <v>7009801</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3892,7 +3903,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3924,10 +3935,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123052141</v>
+        <v>123046193</v>
       </c>
       <c r="B27" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3964,13 +3975,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493514</v>
+        <v>493415</v>
       </c>
       <c r="R27" t="n">
-        <v>7009883</v>
+        <v>7009815</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4033,12 +4044,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4056,10 +4067,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123050424</v>
+        <v>123049755</v>
       </c>
       <c r="B28" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4096,13 +4107,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493465</v>
+        <v>493474</v>
       </c>
       <c r="R28" t="n">
-        <v>7009851</v>
+        <v>7009808</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4132,11 +4143,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4191,7 +4197,7 @@
         <v>123052756</v>
       </c>
       <c r="B29" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4320,10 +4326,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123049318</v>
+        <v>123034670</v>
       </c>
       <c r="B30" t="n">
-        <v>78781</v>
+        <v>57643</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4336,37 +4342,51 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493450</v>
+        <v>493328</v>
       </c>
       <c r="R30" t="n">
-        <v>7009784</v>
+        <v>7009783</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4400,7 +4420,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 2 st talltitor, ev. fler. Fyndplatsen finns i flerskiktad gammal granskog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4415,26 +4435,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123056726</v>
+        <v>123135507</v>
       </c>
       <c r="B31" t="n">
-        <v>91676</v>
+        <v>90988</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4464,25 +4464,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynjelägden, Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4505,7 +4505,7 @@
         <v>7009914</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4535,11 +4535,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4569,12 +4564,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4592,10 +4587,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123135507</v>
+        <v>123056726</v>
       </c>
       <c r="B32" t="n">
-        <v>90983</v>
+        <v>91681</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4604,25 +4599,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4635,7 +4630,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4645,7 +4640,7 @@
         <v>7009914</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4675,6 +4670,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617329</v>
+        <v>123617207</v>
       </c>
       <c r="B33" t="n">
-        <v>57857</v>
+        <v>97367</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,41 +4743,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4786,13 +4772,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493431</v>
+        <v>493466</v>
       </c>
       <c r="R33" t="n">
-        <v>7009773</v>
+        <v>7009777</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4822,11 +4808,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4858,10 +4839,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123616525</v>
+        <v>123616867</v>
       </c>
       <c r="B34" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4903,10 +4884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493367</v>
+        <v>493384</v>
       </c>
       <c r="R34" t="n">
-        <v>7009852</v>
+        <v>7009812</v>
       </c>
       <c r="S34" t="n">
         <v>7</v>
@@ -4970,10 +4951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123616609</v>
+        <v>123617140</v>
       </c>
       <c r="B35" t="n">
-        <v>100662</v>
+        <v>57860</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4986,27 +4967,41 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5015,13 +5010,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493390</v>
+        <v>493469</v>
       </c>
       <c r="R35" t="n">
-        <v>7009845</v>
+        <v>7009816</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5051,6 +5046,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5082,10 +5082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617140</v>
+        <v>123616609</v>
       </c>
       <c r="B36" t="n">
-        <v>57857</v>
+        <v>100680</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5098,41 +5098,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5141,13 +5127,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493469</v>
+        <v>493390</v>
       </c>
       <c r="R36" t="n">
-        <v>7009816</v>
+        <v>7009845</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5177,11 +5163,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5213,10 +5194,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123616867</v>
+        <v>123616525</v>
       </c>
       <c r="B37" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5258,10 +5239,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493384</v>
+        <v>493367</v>
       </c>
       <c r="R37" t="n">
-        <v>7009812</v>
+        <v>7009852</v>
       </c>
       <c r="S37" t="n">
         <v>7</v>
@@ -5325,10 +5306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617207</v>
+        <v>123617329</v>
       </c>
       <c r="B38" t="n">
-        <v>97350</v>
+        <v>57860</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5341,27 +5322,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5370,13 +5365,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493466</v>
+        <v>493431</v>
       </c>
       <c r="R38" t="n">
-        <v>7009777</v>
+        <v>7009773</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5406,6 +5401,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123725484</v>
+        <v>123726570</v>
       </c>
       <c r="B39" t="n">
-        <v>57857</v>
+        <v>57643</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5449,25 +5449,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5475,14 +5475,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5496,13 +5491,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493356</v>
+        <v>493381</v>
       </c>
       <c r="R39" t="n">
-        <v>7009680</v>
+        <v>7009679</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5532,6 +5527,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5563,10 +5563,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123726570</v>
+        <v>123733427</v>
       </c>
       <c r="B40" t="n">
-        <v>57640</v>
+        <v>100680</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5575,35 +5575,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5617,13 +5613,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493381</v>
+        <v>493324</v>
       </c>
       <c r="R40" t="n">
-        <v>7009679</v>
+        <v>7009783</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5653,11 +5649,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5689,10 +5680,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123733427</v>
+        <v>123726856</v>
       </c>
       <c r="B41" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5739,13 +5730,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493324</v>
+        <v>493371</v>
       </c>
       <c r="R41" t="n">
-        <v>7009783</v>
+        <v>7009706</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5806,10 +5797,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123732386</v>
+        <v>123726337</v>
       </c>
       <c r="B42" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5842,7 +5833,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5856,13 +5847,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493374</v>
+        <v>493412</v>
       </c>
       <c r="R42" t="n">
-        <v>7009884</v>
+        <v>7009647</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5923,10 +5914,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123733352</v>
+        <v>123733066</v>
       </c>
       <c r="B43" t="n">
-        <v>100662</v>
+        <v>97367</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5939,21 +5930,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5973,13 +5964,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493302</v>
+        <v>493280</v>
       </c>
       <c r="R43" t="n">
-        <v>7009788</v>
+        <v>7009832</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6040,10 +6031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123727458</v>
+        <v>123732971</v>
       </c>
       <c r="B44" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6090,13 +6081,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493403</v>
+        <v>493336</v>
       </c>
       <c r="R44" t="n">
-        <v>7009782</v>
+        <v>7009883</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6157,10 +6148,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123725306</v>
+        <v>123727458</v>
       </c>
       <c r="B45" t="n">
-        <v>97350</v>
+        <v>100680</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6173,21 +6164,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6196,19 +6187,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493390</v>
+        <v>493403</v>
       </c>
       <c r="R45" t="n">
-        <v>7009685</v>
+        <v>7009782</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6269,10 +6265,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123733095</v>
+        <v>123725949</v>
       </c>
       <c r="B46" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6319,13 +6315,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493278</v>
+        <v>493389</v>
       </c>
       <c r="R46" t="n">
-        <v>7009820</v>
+        <v>7009683</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6386,10 +6382,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123727294</v>
+        <v>123730921</v>
       </c>
       <c r="B47" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6436,13 +6432,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493367</v>
+        <v>493438</v>
       </c>
       <c r="R47" t="n">
-        <v>7009725</v>
+        <v>7009868</v>
       </c>
       <c r="S47" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6485,7 +6481,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6503,10 +6499,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123732971</v>
+        <v>123725484</v>
       </c>
       <c r="B48" t="n">
-        <v>100662</v>
+        <v>57860</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6519,27 +6515,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6553,13 +6558,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493336</v>
+        <v>493356</v>
       </c>
       <c r="R48" t="n">
-        <v>7009883</v>
+        <v>7009680</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6620,10 +6625,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123725818</v>
+        <v>123725306</v>
       </c>
       <c r="B49" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6659,21 +6664,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493368</v>
+        <v>493390</v>
       </c>
       <c r="R49" t="n">
-        <v>7009687</v>
+        <v>7009685</v>
       </c>
       <c r="S49" t="n">
         <v>8</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123733066</v>
+        <v>123733352</v>
       </c>
       <c r="B50" t="n">
-        <v>97350</v>
+        <v>100680</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6753,21 +6753,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493280</v>
+        <v>493302</v>
       </c>
       <c r="R50" t="n">
-        <v>7009832</v>
+        <v>7009788</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6854,10 +6854,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123725949</v>
+        <v>123733095</v>
       </c>
       <c r="B51" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6904,13 +6904,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493389</v>
+        <v>493278</v>
       </c>
       <c r="R51" t="n">
-        <v>7009683</v>
+        <v>7009820</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123733311</v>
+        <v>123730590</v>
       </c>
       <c r="B52" t="n">
-        <v>97350</v>
+        <v>100680</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6987,21 +6987,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7010,16 +7010,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493300</v>
+        <v>493530</v>
       </c>
       <c r="R52" t="n">
-        <v>7009795</v>
+        <v>7009886</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -7065,7 +7070,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7083,10 +7088,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123730921</v>
+        <v>123732386</v>
       </c>
       <c r="B53" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7119,7 +7124,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7133,13 +7138,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493438</v>
+        <v>493374</v>
       </c>
       <c r="R53" t="n">
-        <v>7009868</v>
+        <v>7009884</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7182,7 +7187,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7200,10 +7205,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123726856</v>
+        <v>123727294</v>
       </c>
       <c r="B54" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7250,13 +7255,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493371</v>
+        <v>493367</v>
       </c>
       <c r="R54" t="n">
-        <v>7009706</v>
+        <v>7009725</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7317,10 +7322,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123726337</v>
+        <v>123725818</v>
       </c>
       <c r="B55" t="n">
-        <v>100662</v>
+        <v>97367</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7333,21 +7338,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7367,13 +7372,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493412</v>
+        <v>493368</v>
       </c>
       <c r="R55" t="n">
-        <v>7009647</v>
+        <v>7009687</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7434,10 +7439,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123730590</v>
+        <v>123733311</v>
       </c>
       <c r="B56" t="n">
-        <v>100662</v>
+        <v>97367</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7450,21 +7455,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7473,21 +7478,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493530</v>
+        <v>493300</v>
       </c>
       <c r="R56" t="n">
-        <v>7009886</v>
+        <v>7009795</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123618504</v>
+        <v>123728604</v>
       </c>
       <c r="B57" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7610,13 +7610,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493449</v>
+        <v>493379</v>
       </c>
       <c r="R57" t="n">
-        <v>7009750</v>
+        <v>7009848</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7640,17 +7640,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7682,10 +7682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123619506</v>
+        <v>123732177</v>
       </c>
       <c r="B58" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7715,10 +7715,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -7732,13 +7741,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493457</v>
+        <v>493430</v>
       </c>
       <c r="R58" t="n">
-        <v>7009777</v>
+        <v>7009898</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7762,17 +7771,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7804,10 +7813,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123730088</v>
+        <v>123618504</v>
       </c>
       <c r="B59" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7839,7 +7848,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7863,10 +7872,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493472</v>
+        <v>493449</v>
       </c>
       <c r="R59" t="n">
-        <v>7009838</v>
+        <v>7009750</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -7893,17 +7902,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7917,7 +7926,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7935,10 +7944,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123728604</v>
+        <v>123730088</v>
       </c>
       <c r="B60" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7970,7 +7979,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7994,13 +8003,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493379</v>
+        <v>493472</v>
       </c>
       <c r="R60" t="n">
-        <v>7009848</v>
+        <v>7009838</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8034,7 +8043,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8048,7 +8057,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8069,7 +8078,7 @@
         <v>123725700</v>
       </c>
       <c r="B61" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8197,10 +8206,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123732177</v>
+        <v>123619506</v>
       </c>
       <c r="B62" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8230,19 +8239,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8256,13 +8256,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493430</v>
+        <v>493457</v>
       </c>
       <c r="R62" t="n">
-        <v>7009898</v>
+        <v>7009777</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8286,17 +8286,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -4452,10 +4452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123135507</v>
+        <v>123056726</v>
       </c>
       <c r="B31" t="n">
-        <v>90988</v>
+        <v>91683</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4464,25 +4464,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4505,7 +4505,7 @@
         <v>7009914</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4535,6 +4535,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4564,12 +4569,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4587,10 +4592,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123056726</v>
+        <v>123135507</v>
       </c>
       <c r="B32" t="n">
-        <v>91681</v>
+        <v>90990</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4599,25 +4604,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4630,7 +4635,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brynjelägden, Brynjelägden, Jmt</t>
+          <t>Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4640,7 +4645,7 @@
         <v>7009914</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4670,11 +4675,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en smal granstam som lutar mot en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # En stående/lutande smal granstam som lutar mot en flerstammig sälg. # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617207</v>
+        <v>123617140</v>
       </c>
       <c r="B33" t="n">
-        <v>97367</v>
+        <v>57861</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,27 +4743,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4772,13 +4786,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493466</v>
+        <v>493469</v>
       </c>
       <c r="R33" t="n">
-        <v>7009777</v>
+        <v>7009816</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4808,6 +4822,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4839,10 +4858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123616867</v>
+        <v>123617329</v>
       </c>
       <c r="B34" t="n">
-        <v>100680</v>
+        <v>57861</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4855,27 +4874,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4884,13 +4917,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493384</v>
+        <v>493431</v>
       </c>
       <c r="R34" t="n">
-        <v>7009812</v>
+        <v>7009773</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4920,6 +4953,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4951,10 +4989,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617140</v>
+        <v>123617207</v>
       </c>
       <c r="B35" t="n">
-        <v>57860</v>
+        <v>97369</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4967,41 +5005,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5010,13 +5034,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493469</v>
+        <v>493466</v>
       </c>
       <c r="R35" t="n">
-        <v>7009816</v>
+        <v>7009777</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5046,11 +5070,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5085,7 +5104,7 @@
         <v>123616609</v>
       </c>
       <c r="B36" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5194,10 +5213,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123616525</v>
+        <v>123616867</v>
       </c>
       <c r="B37" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5239,10 +5258,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493367</v>
+        <v>493384</v>
       </c>
       <c r="R37" t="n">
-        <v>7009852</v>
+        <v>7009812</v>
       </c>
       <c r="S37" t="n">
         <v>7</v>
@@ -5306,10 +5325,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617329</v>
+        <v>123616525</v>
       </c>
       <c r="B38" t="n">
-        <v>57860</v>
+        <v>100682</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5322,41 +5341,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5365,13 +5370,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493431</v>
+        <v>493367</v>
       </c>
       <c r="R38" t="n">
-        <v>7009773</v>
+        <v>7009852</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5401,11 +5406,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123726570</v>
+        <v>123725818</v>
       </c>
       <c r="B39" t="n">
-        <v>57643</v>
+        <v>97369</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5449,35 +5449,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5491,13 +5487,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493381</v>
+        <v>493368</v>
       </c>
       <c r="R39" t="n">
-        <v>7009679</v>
+        <v>7009687</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5527,11 +5523,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5563,10 +5554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123733427</v>
+        <v>123730921</v>
       </c>
       <c r="B40" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5613,13 +5604,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493324</v>
+        <v>493438</v>
       </c>
       <c r="R40" t="n">
-        <v>7009783</v>
+        <v>7009868</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5662,7 +5653,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5680,10 +5671,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123726856</v>
+        <v>123727458</v>
       </c>
       <c r="B41" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5730,13 +5721,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493371</v>
+        <v>493403</v>
       </c>
       <c r="R41" t="n">
-        <v>7009706</v>
+        <v>7009782</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5797,10 +5788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123726337</v>
+        <v>123725949</v>
       </c>
       <c r="B42" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5847,13 +5838,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493412</v>
+        <v>493389</v>
       </c>
       <c r="R42" t="n">
-        <v>7009647</v>
+        <v>7009683</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5914,10 +5905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123733066</v>
+        <v>123725306</v>
       </c>
       <c r="B43" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5953,21 +5944,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493280</v>
+        <v>493390</v>
       </c>
       <c r="R43" t="n">
-        <v>7009832</v>
+        <v>7009685</v>
       </c>
       <c r="S43" t="n">
         <v>8</v>
@@ -6031,10 +6017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123732971</v>
+        <v>123733311</v>
       </c>
       <c r="B44" t="n">
-        <v>100680</v>
+        <v>97369</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6047,21 +6033,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6070,21 +6056,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493336</v>
+        <v>493300</v>
       </c>
       <c r="R44" t="n">
-        <v>7009883</v>
+        <v>7009795</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6148,10 +6129,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123727458</v>
+        <v>123733066</v>
       </c>
       <c r="B45" t="n">
-        <v>100680</v>
+        <v>97369</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6164,21 +6145,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6198,13 +6179,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493403</v>
+        <v>493280</v>
       </c>
       <c r="R45" t="n">
-        <v>7009782</v>
+        <v>7009832</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6265,10 +6246,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123725949</v>
+        <v>123726856</v>
       </c>
       <c r="B46" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6315,13 +6296,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493389</v>
+        <v>493371</v>
       </c>
       <c r="R46" t="n">
-        <v>7009683</v>
+        <v>7009706</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6382,10 +6363,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123730921</v>
+        <v>123727294</v>
       </c>
       <c r="B47" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6432,13 +6413,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493438</v>
+        <v>493367</v>
       </c>
       <c r="R47" t="n">
-        <v>7009868</v>
+        <v>7009725</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6481,7 +6462,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6499,10 +6480,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123725484</v>
+        <v>123733427</v>
       </c>
       <c r="B48" t="n">
-        <v>57860</v>
+        <v>100682</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6515,36 +6496,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6558,13 +6530,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493356</v>
+        <v>493324</v>
       </c>
       <c r="R48" t="n">
-        <v>7009680</v>
+        <v>7009783</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6625,10 +6597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123725306</v>
+        <v>123732971</v>
       </c>
       <c r="B49" t="n">
-        <v>97367</v>
+        <v>100682</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6641,21 +6613,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6664,19 +6636,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493390</v>
+        <v>493336</v>
       </c>
       <c r="R49" t="n">
-        <v>7009685</v>
+        <v>7009883</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6737,10 +6714,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123733352</v>
+        <v>123726570</v>
       </c>
       <c r="B50" t="n">
-        <v>100680</v>
+        <v>57644</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6749,31 +6726,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6787,13 +6768,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493302</v>
+        <v>493381</v>
       </c>
       <c r="R50" t="n">
-        <v>7009788</v>
+        <v>7009679</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6823,6 +6804,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6854,10 +6840,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123733095</v>
+        <v>123732386</v>
       </c>
       <c r="B51" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6890,7 +6876,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6904,13 +6890,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493278</v>
+        <v>493374</v>
       </c>
       <c r="R51" t="n">
-        <v>7009820</v>
+        <v>7009884</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6971,10 +6957,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123730590</v>
+        <v>123733095</v>
       </c>
       <c r="B52" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7021,13 +7007,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493530</v>
+        <v>493278</v>
       </c>
       <c r="R52" t="n">
-        <v>7009886</v>
+        <v>7009820</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7070,7 +7056,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7088,10 +7074,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123732386</v>
+        <v>123730590</v>
       </c>
       <c r="B53" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7124,7 +7110,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7138,13 +7124,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493374</v>
+        <v>493530</v>
       </c>
       <c r="R53" t="n">
-        <v>7009884</v>
+        <v>7009886</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7187,7 +7173,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7205,10 +7191,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123727294</v>
+        <v>123733352</v>
       </c>
       <c r="B54" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7255,13 +7241,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493367</v>
+        <v>493302</v>
       </c>
       <c r="R54" t="n">
-        <v>7009725</v>
+        <v>7009788</v>
       </c>
       <c r="S54" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7322,10 +7308,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123725818</v>
+        <v>123725484</v>
       </c>
       <c r="B55" t="n">
-        <v>97367</v>
+        <v>57861</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7338,27 +7324,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7372,13 +7367,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493368</v>
+        <v>493356</v>
       </c>
       <c r="R55" t="n">
-        <v>7009687</v>
+        <v>7009680</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7439,10 +7434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123733311</v>
+        <v>123726337</v>
       </c>
       <c r="B56" t="n">
-        <v>97367</v>
+        <v>100682</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7455,21 +7450,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7478,19 +7473,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493300</v>
+        <v>493412</v>
       </c>
       <c r="R56" t="n">
-        <v>7009795</v>
+        <v>7009647</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123728604</v>
+        <v>123732177</v>
       </c>
       <c r="B57" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7610,13 +7610,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493379</v>
+        <v>493430</v>
       </c>
       <c r="R57" t="n">
-        <v>7009848</v>
+        <v>7009898</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7682,10 +7682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123732177</v>
+        <v>123725700</v>
       </c>
       <c r="B58" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493430</v>
+        <v>493341</v>
       </c>
       <c r="R58" t="n">
-        <v>7009898</v>
+        <v>7009682</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7813,10 +7813,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123618504</v>
+        <v>123619506</v>
       </c>
       <c r="B59" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7846,19 +7846,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -7872,13 +7863,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493449</v>
+        <v>493457</v>
       </c>
       <c r="R59" t="n">
-        <v>7009750</v>
+        <v>7009777</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7912,7 +7903,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7944,10 +7935,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123730088</v>
+        <v>123728604</v>
       </c>
       <c r="B60" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7979,7 +7970,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8003,13 +7994,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493472</v>
+        <v>493379</v>
       </c>
       <c r="R60" t="n">
-        <v>7009838</v>
+        <v>7009848</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8043,7 +8034,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
+          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8057,7 +8048,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8075,10 +8066,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123725700</v>
+        <v>123730088</v>
       </c>
       <c r="B61" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8110,7 +8101,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8134,10 +8125,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>493341</v>
+        <v>493472</v>
       </c>
       <c r="R61" t="n">
-        <v>7009682</v>
+        <v>7009838</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -8174,7 +8165,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
+          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8188,7 +8179,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8206,10 +8197,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123619506</v>
+        <v>123618504</v>
       </c>
       <c r="B62" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8239,10 +8230,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8256,13 +8256,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493457</v>
+        <v>493449</v>
       </c>
       <c r="R62" t="n">
-        <v>7009777</v>
+        <v>7009750</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -4727,10 +4727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617140</v>
+        <v>123616609</v>
       </c>
       <c r="B33" t="n">
-        <v>57861</v>
+        <v>100257</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,41 +4743,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4786,13 +4772,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493469</v>
+        <v>493390</v>
       </c>
       <c r="R33" t="n">
-        <v>7009816</v>
+        <v>7009845</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4822,11 +4808,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4858,7 +4839,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617329</v>
+        <v>123617140</v>
       </c>
       <c r="B34" t="n">
         <v>57861</v>
@@ -4917,13 +4898,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493431</v>
+        <v>493469</v>
       </c>
       <c r="R34" t="n">
-        <v>7009773</v>
+        <v>7009816</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4957,7 +4938,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>I flerskiktad gammal granskog.</t>
+          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4989,10 +4970,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617207</v>
+        <v>123616525</v>
       </c>
       <c r="B35" t="n">
-        <v>97369</v>
+        <v>100257</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5005,21 +4986,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5034,13 +5015,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493466</v>
+        <v>493367</v>
       </c>
       <c r="R35" t="n">
-        <v>7009777</v>
+        <v>7009852</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5101,10 +5082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123616609</v>
+        <v>123617329</v>
       </c>
       <c r="B36" t="n">
-        <v>100682</v>
+        <v>57861</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5117,27 +5098,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5146,13 +5141,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493390</v>
+        <v>493431</v>
       </c>
       <c r="R36" t="n">
-        <v>7009845</v>
+        <v>7009773</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5182,6 +5177,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5216,7 +5216,7 @@
         <v>123616867</v>
       </c>
       <c r="B37" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123616525</v>
+        <v>123617207</v>
       </c>
       <c r="B38" t="n">
-        <v>100682</v>
+        <v>96957</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5341,21 +5341,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5370,13 +5370,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493367</v>
+        <v>493466</v>
       </c>
       <c r="R38" t="n">
-        <v>7009852</v>
+        <v>7009777</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5437,10 +5437,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123725818</v>
+        <v>123730921</v>
       </c>
       <c r="B39" t="n">
-        <v>97369</v>
+        <v>100257</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5453,21 +5453,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5487,13 +5487,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493368</v>
+        <v>493438</v>
       </c>
       <c r="R39" t="n">
-        <v>7009687</v>
+        <v>7009868</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123730921</v>
+        <v>123725949</v>
       </c>
       <c r="B40" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5604,13 +5604,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493438</v>
+        <v>493389</v>
       </c>
       <c r="R40" t="n">
-        <v>7009868</v>
+        <v>7009683</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5674,7 +5674,7 @@
         <v>123727458</v>
       </c>
       <c r="B41" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123725949</v>
+        <v>123733311</v>
       </c>
       <c r="B42" t="n">
-        <v>100682</v>
+        <v>96957</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5804,21 +5804,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5827,24 +5827,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493389</v>
+        <v>493300</v>
       </c>
       <c r="R42" t="n">
-        <v>7009683</v>
+        <v>7009795</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5905,10 +5900,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123725306</v>
+        <v>123725484</v>
       </c>
       <c r="B43" t="n">
-        <v>97369</v>
+        <v>57861</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5921,27 +5916,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5950,13 +5959,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493390</v>
+        <v>493356</v>
       </c>
       <c r="R43" t="n">
-        <v>7009685</v>
+        <v>7009680</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6017,10 +6026,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123733311</v>
+        <v>123732971</v>
       </c>
       <c r="B44" t="n">
-        <v>97369</v>
+        <v>100257</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6033,21 +6042,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6056,16 +6065,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493300</v>
+        <v>493336</v>
       </c>
       <c r="R44" t="n">
-        <v>7009795</v>
+        <v>7009883</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6129,10 +6143,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123733066</v>
+        <v>123726337</v>
       </c>
       <c r="B45" t="n">
-        <v>97369</v>
+        <v>100257</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6145,21 +6159,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6179,13 +6193,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493280</v>
+        <v>493412</v>
       </c>
       <c r="R45" t="n">
-        <v>7009832</v>
+        <v>7009647</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6246,10 +6260,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123726856</v>
+        <v>123730590</v>
       </c>
       <c r="B46" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6296,10 +6310,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493371</v>
+        <v>493530</v>
       </c>
       <c r="R46" t="n">
-        <v>7009706</v>
+        <v>7009886</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -6345,7 +6359,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6363,10 +6377,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123727294</v>
+        <v>123725306</v>
       </c>
       <c r="B47" t="n">
-        <v>100682</v>
+        <v>96957</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6379,21 +6393,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6402,24 +6416,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493367</v>
+        <v>493390</v>
       </c>
       <c r="R47" t="n">
-        <v>7009725</v>
+        <v>7009685</v>
       </c>
       <c r="S47" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6480,10 +6489,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123733427</v>
+        <v>123732386</v>
       </c>
       <c r="B48" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6516,7 +6525,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6530,10 +6539,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493324</v>
+        <v>493374</v>
       </c>
       <c r="R48" t="n">
-        <v>7009783</v>
+        <v>7009884</v>
       </c>
       <c r="S48" t="n">
         <v>8</v>
@@ -6597,10 +6606,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123732971</v>
+        <v>123726856</v>
       </c>
       <c r="B49" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6647,10 +6656,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493336</v>
+        <v>493371</v>
       </c>
       <c r="R49" t="n">
-        <v>7009883</v>
+        <v>7009706</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6714,10 +6723,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123726570</v>
+        <v>123733352</v>
       </c>
       <c r="B50" t="n">
-        <v>57644</v>
+        <v>100257</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6726,35 +6735,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6768,13 +6773,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493381</v>
+        <v>493302</v>
       </c>
       <c r="R50" t="n">
-        <v>7009679</v>
+        <v>7009788</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6804,11 +6809,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6840,10 +6840,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123732386</v>
+        <v>123725818</v>
       </c>
       <c r="B51" t="n">
-        <v>100682</v>
+        <v>96957</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6856,27 +6856,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493374</v>
+        <v>493368</v>
       </c>
       <c r="R51" t="n">
-        <v>7009884</v>
+        <v>7009687</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
@@ -6957,10 +6957,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123733095</v>
+        <v>123733427</v>
       </c>
       <c r="B52" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7007,13 +7007,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493278</v>
+        <v>493324</v>
       </c>
       <c r="R52" t="n">
-        <v>7009820</v>
+        <v>7009783</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123730590</v>
+        <v>123727294</v>
       </c>
       <c r="B53" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493530</v>
+        <v>493367</v>
       </c>
       <c r="R53" t="n">
-        <v>7009886</v>
+        <v>7009725</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7191,10 +7191,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123733352</v>
+        <v>123726570</v>
       </c>
       <c r="B54" t="n">
-        <v>100682</v>
+        <v>57644</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7203,31 +7203,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7241,13 +7245,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493302</v>
+        <v>493381</v>
       </c>
       <c r="R54" t="n">
-        <v>7009788</v>
+        <v>7009679</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7277,6 +7281,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7308,10 +7317,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123725484</v>
+        <v>123733066</v>
       </c>
       <c r="B55" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7324,36 +7333,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493356</v>
+        <v>493280</v>
       </c>
       <c r="R55" t="n">
-        <v>7009680</v>
+        <v>7009832</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123726337</v>
+        <v>123733095</v>
       </c>
       <c r="B56" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7484,13 +7484,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493412</v>
+        <v>493278</v>
       </c>
       <c r="R56" t="n">
-        <v>7009647</v>
+        <v>7009820</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123732177</v>
+        <v>123618504</v>
       </c>
       <c r="B57" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493430</v>
+        <v>493449</v>
       </c>
       <c r="R57" t="n">
-        <v>7009898</v>
+        <v>7009750</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7640,17 +7640,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7682,10 +7682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123725700</v>
+        <v>123730088</v>
       </c>
       <c r="B58" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493341</v>
+        <v>493472</v>
       </c>
       <c r="R58" t="n">
-        <v>7009682</v>
+        <v>7009838</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
+          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7813,10 +7813,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123619506</v>
+        <v>123728604</v>
       </c>
       <c r="B59" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7846,10 +7846,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -7863,13 +7872,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493457</v>
+        <v>493379</v>
       </c>
       <c r="R59" t="n">
-        <v>7009777</v>
+        <v>7009848</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7893,17 +7902,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7935,10 +7944,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123728604</v>
+        <v>123619506</v>
       </c>
       <c r="B60" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7968,19 +7977,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -7994,13 +7994,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493379</v>
+        <v>493457</v>
       </c>
       <c r="R60" t="n">
-        <v>7009848</v>
+        <v>7009777</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8024,17 +8024,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8066,10 +8066,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123730088</v>
+        <v>123732177</v>
       </c>
       <c r="B61" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>493472</v>
+        <v>493430</v>
       </c>
       <c r="R61" t="n">
-        <v>7009838</v>
+        <v>7009898</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
+          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8197,10 +8197,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123618504</v>
+        <v>123725700</v>
       </c>
       <c r="B62" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8256,10 +8256,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493449</v>
+        <v>493341</v>
       </c>
       <c r="R62" t="n">
-        <v>7009750</v>
+        <v>7009682</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -8286,17 +8286,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -4727,10 +4727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123616609</v>
+        <v>123617329</v>
       </c>
       <c r="B33" t="n">
-        <v>100257</v>
+        <v>57861</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,27 +4743,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4772,13 +4786,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493390</v>
+        <v>493431</v>
       </c>
       <c r="R33" t="n">
-        <v>7009845</v>
+        <v>7009773</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4808,6 +4822,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4839,10 +4858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617140</v>
+        <v>123616609</v>
       </c>
       <c r="B34" t="n">
-        <v>57861</v>
+        <v>100257</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4855,41 +4874,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4898,13 +4903,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493469</v>
+        <v>493390</v>
       </c>
       <c r="R34" t="n">
-        <v>7009816</v>
+        <v>7009845</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4934,11 +4939,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5082,7 +5082,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617329</v>
+        <v>123617140</v>
       </c>
       <c r="B36" t="n">
         <v>57861</v>
@@ -5141,13 +5141,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493431</v>
+        <v>493469</v>
       </c>
       <c r="R36" t="n">
-        <v>7009773</v>
+        <v>7009816</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I flerskiktad gammal granskog.</t>
+          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5213,10 +5213,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123616867</v>
+        <v>123617207</v>
       </c>
       <c r="B37" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5229,21 +5229,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5258,13 +5258,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493384</v>
+        <v>493466</v>
       </c>
       <c r="R37" t="n">
-        <v>7009812</v>
+        <v>7009777</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617207</v>
+        <v>123616867</v>
       </c>
       <c r="B38" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5341,21 +5341,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5370,13 +5370,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493466</v>
+        <v>493384</v>
       </c>
       <c r="R38" t="n">
-        <v>7009777</v>
+        <v>7009812</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123730921</v>
+        <v>123726337</v>
       </c>
       <c r="B39" t="n">
         <v>100257</v>
@@ -5487,13 +5487,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493438</v>
+        <v>493412</v>
       </c>
       <c r="R39" t="n">
-        <v>7009868</v>
+        <v>7009647</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123725949</v>
+        <v>123727458</v>
       </c>
       <c r="B40" t="n">
         <v>100257</v>
@@ -5604,13 +5604,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493389</v>
+        <v>493403</v>
       </c>
       <c r="R40" t="n">
-        <v>7009683</v>
+        <v>7009782</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123727458</v>
+        <v>123730921</v>
       </c>
       <c r="B41" t="n">
         <v>100257</v>
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493403</v>
+        <v>493438</v>
       </c>
       <c r="R41" t="n">
-        <v>7009782</v>
+        <v>7009868</v>
       </c>
       <c r="S41" t="n">
         <v>11</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123733311</v>
+        <v>123732971</v>
       </c>
       <c r="B42" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5804,21 +5804,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5827,16 +5827,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493300</v>
+        <v>493336</v>
       </c>
       <c r="R42" t="n">
-        <v>7009795</v>
+        <v>7009883</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5900,10 +5905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123725484</v>
+        <v>123733352</v>
       </c>
       <c r="B43" t="n">
-        <v>57861</v>
+        <v>100257</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5916,36 +5921,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5959,13 +5955,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493356</v>
+        <v>493302</v>
       </c>
       <c r="R43" t="n">
-        <v>7009680</v>
+        <v>7009788</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6026,7 +6022,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123732971</v>
+        <v>123725949</v>
       </c>
       <c r="B44" t="n">
         <v>100257</v>
@@ -6076,13 +6072,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493336</v>
+        <v>493389</v>
       </c>
       <c r="R44" t="n">
-        <v>7009883</v>
+        <v>7009683</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6143,7 +6139,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123726337</v>
+        <v>123732386</v>
       </c>
       <c r="B45" t="n">
         <v>100257</v>
@@ -6179,7 +6175,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6193,13 +6189,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493412</v>
+        <v>493374</v>
       </c>
       <c r="R45" t="n">
-        <v>7009647</v>
+        <v>7009884</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6260,10 +6256,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123730590</v>
+        <v>123725818</v>
       </c>
       <c r="B46" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6276,21 +6272,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6310,13 +6306,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493530</v>
+        <v>493368</v>
       </c>
       <c r="R46" t="n">
-        <v>7009886</v>
+        <v>7009687</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6359,7 +6355,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6377,10 +6373,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123725306</v>
+        <v>123727294</v>
       </c>
       <c r="B47" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6393,21 +6389,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6416,19 +6412,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493390</v>
+        <v>493367</v>
       </c>
       <c r="R47" t="n">
-        <v>7009685</v>
+        <v>7009725</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6489,10 +6490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123732386</v>
+        <v>123733311</v>
       </c>
       <c r="B48" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6505,32 +6506,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6539,13 +6535,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493374</v>
+        <v>493300</v>
       </c>
       <c r="R48" t="n">
-        <v>7009884</v>
+        <v>7009795</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6606,7 +6602,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123726856</v>
+        <v>123733095</v>
       </c>
       <c r="B49" t="n">
         <v>100257</v>
@@ -6656,13 +6652,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493371</v>
+        <v>493278</v>
       </c>
       <c r="R49" t="n">
-        <v>7009706</v>
+        <v>7009820</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6723,10 +6719,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123733352</v>
+        <v>123725484</v>
       </c>
       <c r="B50" t="n">
-        <v>100257</v>
+        <v>57861</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6739,27 +6735,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6773,13 +6778,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493302</v>
+        <v>493356</v>
       </c>
       <c r="R50" t="n">
-        <v>7009788</v>
+        <v>7009680</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6840,10 +6845,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123725818</v>
+        <v>123730590</v>
       </c>
       <c r="B51" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6856,21 +6861,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6890,13 +6895,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493368</v>
+        <v>493530</v>
       </c>
       <c r="R51" t="n">
-        <v>7009687</v>
+        <v>7009886</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6939,7 +6944,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7074,10 +7079,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123727294</v>
+        <v>123733066</v>
       </c>
       <c r="B53" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7090,21 +7095,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7124,13 +7129,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493367</v>
+        <v>493280</v>
       </c>
       <c r="R53" t="n">
-        <v>7009725</v>
+        <v>7009832</v>
       </c>
       <c r="S53" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7191,10 +7196,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123726570</v>
+        <v>123725306</v>
       </c>
       <c r="B54" t="n">
-        <v>57644</v>
+        <v>96957</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7203,40 +7208,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7245,13 +7241,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493381</v>
+        <v>493390</v>
       </c>
       <c r="R54" t="n">
-        <v>7009679</v>
+        <v>7009685</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7281,11 +7277,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7317,10 +7308,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123733066</v>
+        <v>123726856</v>
       </c>
       <c r="B55" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7333,21 +7324,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7367,13 +7358,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493280</v>
+        <v>493371</v>
       </c>
       <c r="R55" t="n">
-        <v>7009832</v>
+        <v>7009706</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7434,10 +7425,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123733095</v>
+        <v>123726570</v>
       </c>
       <c r="B56" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7446,31 +7437,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7484,13 +7479,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493278</v>
+        <v>493381</v>
       </c>
       <c r="R56" t="n">
-        <v>7009820</v>
+        <v>7009679</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7520,6 +7515,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7551,7 +7551,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123618504</v>
+        <v>123732177</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493449</v>
+        <v>493430</v>
       </c>
       <c r="R57" t="n">
-        <v>7009750</v>
+        <v>7009898</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7640,17 +7640,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7682,7 +7682,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123730088</v>
+        <v>123725700</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493472</v>
+        <v>493341</v>
       </c>
       <c r="R58" t="n">
-        <v>7009838</v>
+        <v>7009682</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
+          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7813,7 +7813,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123728604</v>
+        <v>123730088</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7872,13 +7872,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493379</v>
+        <v>493472</v>
       </c>
       <c r="R59" t="n">
-        <v>7009848</v>
+        <v>7009838</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7944,7 +7944,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123619506</v>
+        <v>123618504</v>
       </c>
       <c r="B60" t="n">
         <v>98079</v>
@@ -7977,10 +7977,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -7994,13 +8003,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493457</v>
+        <v>493449</v>
       </c>
       <c r="R60" t="n">
-        <v>7009777</v>
+        <v>7009750</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8034,7 +8043,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8066,7 +8075,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123732177</v>
+        <v>123619506</v>
       </c>
       <c r="B61" t="n">
         <v>98079</v>
@@ -8099,19 +8108,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>493430</v>
+        <v>493457</v>
       </c>
       <c r="R61" t="n">
-        <v>7009898</v>
+        <v>7009777</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8155,17 +8155,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8197,7 +8197,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123725700</v>
+        <v>123728604</v>
       </c>
       <c r="B62" t="n">
         <v>98079</v>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8256,13 +8256,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493341</v>
+        <v>493379</v>
       </c>
       <c r="R62" t="n">
-        <v>7009682</v>
+        <v>7009848</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
+          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -4727,10 +4727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617329</v>
+        <v>123616867</v>
       </c>
       <c r="B33" t="n">
-        <v>57861</v>
+        <v>100257</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,41 +4743,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4786,13 +4772,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493431</v>
+        <v>493384</v>
       </c>
       <c r="R33" t="n">
-        <v>7009773</v>
+        <v>7009812</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4822,11 +4808,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4858,10 +4839,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123616609</v>
+        <v>123617329</v>
       </c>
       <c r="B34" t="n">
-        <v>100257</v>
+        <v>57861</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4874,27 +4855,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4903,13 +4898,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493390</v>
+        <v>493431</v>
       </c>
       <c r="R34" t="n">
-        <v>7009845</v>
+        <v>7009773</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4939,6 +4934,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5082,10 +5082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617140</v>
+        <v>123616609</v>
       </c>
       <c r="B36" t="n">
-        <v>57861</v>
+        <v>100257</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5098,41 +5098,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5141,13 +5127,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493469</v>
+        <v>493390</v>
       </c>
       <c r="R36" t="n">
-        <v>7009816</v>
+        <v>7009845</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5177,11 +5163,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5325,10 +5306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123616867</v>
+        <v>123617140</v>
       </c>
       <c r="B38" t="n">
-        <v>100257</v>
+        <v>57861</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5341,27 +5322,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5370,13 +5365,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493384</v>
+        <v>493469</v>
       </c>
       <c r="R38" t="n">
-        <v>7009812</v>
+        <v>7009816</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5406,6 +5401,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5437,7 +5437,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123726337</v>
+        <v>123726856</v>
       </c>
       <c r="B39" t="n">
         <v>100257</v>
@@ -5487,13 +5487,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493412</v>
+        <v>493371</v>
       </c>
       <c r="R39" t="n">
-        <v>7009647</v>
+        <v>7009706</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123727458</v>
+        <v>123733352</v>
       </c>
       <c r="B40" t="n">
         <v>100257</v>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493403</v>
+        <v>493302</v>
       </c>
       <c r="R40" t="n">
-        <v>7009782</v>
+        <v>7009788</v>
       </c>
       <c r="S40" t="n">
         <v>11</v>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123732971</v>
+        <v>123726337</v>
       </c>
       <c r="B42" t="n">
         <v>100257</v>
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493336</v>
+        <v>493412</v>
       </c>
       <c r="R42" t="n">
-        <v>7009883</v>
+        <v>7009647</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123733352</v>
+        <v>123733311</v>
       </c>
       <c r="B43" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5921,21 +5921,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5944,24 +5944,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493302</v>
+        <v>493300</v>
       </c>
       <c r="R43" t="n">
-        <v>7009788</v>
+        <v>7009795</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6022,10 +6017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123725949</v>
+        <v>123733066</v>
       </c>
       <c r="B44" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6038,21 +6033,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6072,10 +6067,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493389</v>
+        <v>493280</v>
       </c>
       <c r="R44" t="n">
-        <v>7009683</v>
+        <v>7009832</v>
       </c>
       <c r="S44" t="n">
         <v>8</v>
@@ -6139,7 +6134,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123732386</v>
+        <v>123732971</v>
       </c>
       <c r="B45" t="n">
         <v>100257</v>
@@ -6175,7 +6170,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6189,13 +6184,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493374</v>
+        <v>493336</v>
       </c>
       <c r="R45" t="n">
-        <v>7009884</v>
+        <v>7009883</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6256,10 +6251,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123725818</v>
+        <v>123725484</v>
       </c>
       <c r="B46" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6272,27 +6267,36 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6306,13 +6310,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493368</v>
+        <v>493356</v>
       </c>
       <c r="R46" t="n">
-        <v>7009687</v>
+        <v>7009680</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6373,7 +6377,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123727294</v>
+        <v>123733427</v>
       </c>
       <c r="B47" t="n">
         <v>100257</v>
@@ -6423,13 +6427,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493367</v>
+        <v>493324</v>
       </c>
       <c r="R47" t="n">
-        <v>7009725</v>
+        <v>7009783</v>
       </c>
       <c r="S47" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6490,10 +6494,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123733311</v>
+        <v>123726570</v>
       </c>
       <c r="B48" t="n">
-        <v>96957</v>
+        <v>57644</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6502,31 +6506,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6535,13 +6548,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493300</v>
+        <v>493381</v>
       </c>
       <c r="R48" t="n">
-        <v>7009795</v>
+        <v>7009679</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6571,6 +6584,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6602,7 +6620,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123733095</v>
+        <v>123727458</v>
       </c>
       <c r="B49" t="n">
         <v>100257</v>
@@ -6652,13 +6670,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493278</v>
+        <v>493403</v>
       </c>
       <c r="R49" t="n">
-        <v>7009820</v>
+        <v>7009782</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6719,10 +6737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123725484</v>
+        <v>123725306</v>
       </c>
       <c r="B50" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6735,41 +6753,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6778,13 +6782,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493356</v>
+        <v>493390</v>
       </c>
       <c r="R50" t="n">
-        <v>7009680</v>
+        <v>7009685</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6845,7 +6849,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123730590</v>
+        <v>123732386</v>
       </c>
       <c r="B51" t="n">
         <v>100257</v>
@@ -6881,7 +6885,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6895,13 +6899,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493530</v>
+        <v>493374</v>
       </c>
       <c r="R51" t="n">
-        <v>7009886</v>
+        <v>7009884</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6944,7 +6948,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6962,7 +6966,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123733427</v>
+        <v>123725949</v>
       </c>
       <c r="B52" t="n">
         <v>100257</v>
@@ -7012,10 +7016,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493324</v>
+        <v>493389</v>
       </c>
       <c r="R52" t="n">
-        <v>7009783</v>
+        <v>7009683</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -7079,10 +7083,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123733066</v>
+        <v>123727294</v>
       </c>
       <c r="B53" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7095,21 +7099,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7129,13 +7133,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493280</v>
+        <v>493367</v>
       </c>
       <c r="R53" t="n">
-        <v>7009832</v>
+        <v>7009725</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7196,10 +7200,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123725306</v>
+        <v>123733095</v>
       </c>
       <c r="B54" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7212,21 +7216,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7235,19 +7239,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493390</v>
+        <v>493278</v>
       </c>
       <c r="R54" t="n">
-        <v>7009685</v>
+        <v>7009820</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7308,7 +7317,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123726856</v>
+        <v>123730590</v>
       </c>
       <c r="B55" t="n">
         <v>100257</v>
@@ -7358,10 +7367,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493371</v>
+        <v>493530</v>
       </c>
       <c r="R55" t="n">
-        <v>7009706</v>
+        <v>7009886</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -7407,7 +7416,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7425,10 +7434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123726570</v>
+        <v>123725818</v>
       </c>
       <c r="B56" t="n">
-        <v>57644</v>
+        <v>96957</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7437,35 +7446,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7479,13 +7484,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493381</v>
+        <v>493368</v>
       </c>
       <c r="R56" t="n">
-        <v>7009679</v>
+        <v>7009687</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7515,11 +7520,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7682,7 +7682,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123725700</v>
+        <v>123728604</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493341</v>
+        <v>493379</v>
       </c>
       <c r="R58" t="n">
-        <v>7009682</v>
+        <v>7009848</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
+          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7944,7 +7944,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123618504</v>
+        <v>123619506</v>
       </c>
       <c r="B60" t="n">
         <v>98079</v>
@@ -7977,19 +7977,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8003,13 +7994,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493449</v>
+        <v>493457</v>
       </c>
       <c r="R60" t="n">
-        <v>7009750</v>
+        <v>7009777</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8043,7 +8034,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8075,7 +8066,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123619506</v>
+        <v>123618504</v>
       </c>
       <c r="B61" t="n">
         <v>98079</v>
@@ -8108,10 +8099,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>493457</v>
+        <v>493449</v>
       </c>
       <c r="R61" t="n">
-        <v>7009777</v>
+        <v>7009750</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8197,7 +8197,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123728604</v>
+        <v>123725700</v>
       </c>
       <c r="B62" t="n">
         <v>98079</v>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8256,13 +8256,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493379</v>
+        <v>493341</v>
       </c>
       <c r="R62" t="n">
-        <v>7009848</v>
+        <v>7009682</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -4727,7 +4727,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123616867</v>
+        <v>123616609</v>
       </c>
       <c r="B33" t="n">
         <v>100257</v>
@@ -4772,13 +4772,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493384</v>
+        <v>493390</v>
       </c>
       <c r="R33" t="n">
-        <v>7009812</v>
+        <v>7009845</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4839,10 +4839,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617329</v>
+        <v>123616867</v>
       </c>
       <c r="B34" t="n">
-        <v>57861</v>
+        <v>100257</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4855,41 +4855,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4898,13 +4884,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493431</v>
+        <v>493384</v>
       </c>
       <c r="R34" t="n">
-        <v>7009773</v>
+        <v>7009812</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4934,11 +4920,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4970,10 +4951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123616525</v>
+        <v>123617207</v>
       </c>
       <c r="B35" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4986,21 +4967,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5015,13 +4996,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493367</v>
+        <v>493466</v>
       </c>
       <c r="R35" t="n">
-        <v>7009852</v>
+        <v>7009777</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5082,7 +5063,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123616609</v>
+        <v>123616525</v>
       </c>
       <c r="B36" t="n">
         <v>100257</v>
@@ -5127,13 +5108,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493390</v>
+        <v>493367</v>
       </c>
       <c r="R36" t="n">
-        <v>7009845</v>
+        <v>7009852</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5194,10 +5175,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617207</v>
+        <v>123617329</v>
       </c>
       <c r="B37" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5210,27 +5191,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5239,13 +5234,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493466</v>
+        <v>493431</v>
       </c>
       <c r="R37" t="n">
-        <v>7009777</v>
+        <v>7009773</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5275,6 +5270,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5437,7 +5437,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123726856</v>
+        <v>123726337</v>
       </c>
       <c r="B39" t="n">
         <v>100257</v>
@@ -5487,13 +5487,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493371</v>
+        <v>493412</v>
       </c>
       <c r="R39" t="n">
-        <v>7009706</v>
+        <v>7009647</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123733352</v>
+        <v>123733427</v>
       </c>
       <c r="B40" t="n">
         <v>100257</v>
@@ -5604,13 +5604,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493302</v>
+        <v>493324</v>
       </c>
       <c r="R40" t="n">
-        <v>7009788</v>
+        <v>7009783</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5671,10 +5671,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123730921</v>
+        <v>123725484</v>
       </c>
       <c r="B41" t="n">
-        <v>100257</v>
+        <v>57861</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5687,27 +5687,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5721,13 +5730,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493438</v>
+        <v>493356</v>
       </c>
       <c r="R41" t="n">
-        <v>7009868</v>
+        <v>7009680</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5770,7 +5779,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5788,7 +5797,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123726337</v>
+        <v>123727294</v>
       </c>
       <c r="B42" t="n">
         <v>100257</v>
@@ -5838,13 +5847,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493412</v>
+        <v>493367</v>
       </c>
       <c r="R42" t="n">
-        <v>7009647</v>
+        <v>7009725</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5905,10 +5914,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123733311</v>
+        <v>123732386</v>
       </c>
       <c r="B43" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5921,27 +5930,32 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5950,13 +5964,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493300</v>
+        <v>493374</v>
       </c>
       <c r="R43" t="n">
-        <v>7009795</v>
+        <v>7009884</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6017,10 +6031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123733066</v>
+        <v>123727458</v>
       </c>
       <c r="B44" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6033,21 +6047,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6067,13 +6081,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493280</v>
+        <v>493403</v>
       </c>
       <c r="R44" t="n">
-        <v>7009832</v>
+        <v>7009782</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6134,10 +6148,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123732971</v>
+        <v>123733066</v>
       </c>
       <c r="B45" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6150,21 +6164,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6184,13 +6198,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493336</v>
+        <v>493280</v>
       </c>
       <c r="R45" t="n">
-        <v>7009883</v>
+        <v>7009832</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6251,10 +6265,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123725484</v>
+        <v>123732971</v>
       </c>
       <c r="B46" t="n">
-        <v>57861</v>
+        <v>100257</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6267,36 +6281,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6310,13 +6315,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493356</v>
+        <v>493336</v>
       </c>
       <c r="R46" t="n">
-        <v>7009680</v>
+        <v>7009883</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6377,10 +6382,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123733427</v>
+        <v>123726570</v>
       </c>
       <c r="B47" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6389,31 +6394,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6427,13 +6436,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493324</v>
+        <v>493381</v>
       </c>
       <c r="R47" t="n">
-        <v>7009783</v>
+        <v>7009679</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6463,6 +6472,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6494,10 +6508,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123726570</v>
+        <v>123725306</v>
       </c>
       <c r="B48" t="n">
-        <v>57644</v>
+        <v>96957</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6506,40 +6520,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6548,13 +6553,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493381</v>
+        <v>493390</v>
       </c>
       <c r="R48" t="n">
-        <v>7009679</v>
+        <v>7009685</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6584,11 +6589,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6620,7 +6620,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123727458</v>
+        <v>123725949</v>
       </c>
       <c r="B49" t="n">
         <v>100257</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493403</v>
+        <v>493389</v>
       </c>
       <c r="R49" t="n">
-        <v>7009782</v>
+        <v>7009683</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123725306</v>
+        <v>123725818</v>
       </c>
       <c r="B50" t="n">
         <v>96957</v>
@@ -6776,16 +6776,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493390</v>
+        <v>493368</v>
       </c>
       <c r="R50" t="n">
-        <v>7009685</v>
+        <v>7009687</v>
       </c>
       <c r="S50" t="n">
         <v>8</v>
@@ -6849,10 +6854,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123732386</v>
+        <v>123733311</v>
       </c>
       <c r="B51" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6865,32 +6870,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6899,13 +6899,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493374</v>
+        <v>493300</v>
       </c>
       <c r="R51" t="n">
-        <v>7009884</v>
+        <v>7009795</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123725949</v>
+        <v>123730921</v>
       </c>
       <c r="B52" t="n">
         <v>100257</v>
@@ -7016,13 +7016,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493389</v>
+        <v>493438</v>
       </c>
       <c r="R52" t="n">
-        <v>7009683</v>
+        <v>7009868</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7083,7 +7083,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123727294</v>
+        <v>123733095</v>
       </c>
       <c r="B53" t="n">
         <v>100257</v>
@@ -7133,13 +7133,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493367</v>
+        <v>493278</v>
       </c>
       <c r="R53" t="n">
-        <v>7009725</v>
+        <v>7009820</v>
       </c>
       <c r="S53" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123733095</v>
+        <v>123730590</v>
       </c>
       <c r="B54" t="n">
         <v>100257</v>
@@ -7250,13 +7250,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493278</v>
+        <v>493530</v>
       </c>
       <c r="R54" t="n">
-        <v>7009820</v>
+        <v>7009886</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7317,7 +7317,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123730590</v>
+        <v>123733352</v>
       </c>
       <c r="B55" t="n">
         <v>100257</v>
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493530</v>
+        <v>493302</v>
       </c>
       <c r="R55" t="n">
-        <v>7009886</v>
+        <v>7009788</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123725818</v>
+        <v>123726856</v>
       </c>
       <c r="B56" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7450,21 +7450,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7484,13 +7484,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493368</v>
+        <v>493371</v>
       </c>
       <c r="R56" t="n">
-        <v>7009687</v>
+        <v>7009706</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123732177</v>
+        <v>123730088</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493430</v>
+        <v>493472</v>
       </c>
       <c r="R57" t="n">
-        <v>7009898</v>
+        <v>7009838</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123728604</v>
+        <v>123732177</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493379</v>
+        <v>493430</v>
       </c>
       <c r="R58" t="n">
-        <v>7009848</v>
+        <v>7009898</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7813,7 +7813,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123730088</v>
+        <v>123725700</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493472</v>
+        <v>493341</v>
       </c>
       <c r="R59" t="n">
-        <v>7009838</v>
+        <v>7009682</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
+          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7944,7 +7944,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123619506</v>
+        <v>123618504</v>
       </c>
       <c r="B60" t="n">
         <v>98079</v>
@@ -7977,10 +7977,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -7994,13 +8003,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493457</v>
+        <v>493449</v>
       </c>
       <c r="R60" t="n">
-        <v>7009777</v>
+        <v>7009750</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8034,7 +8043,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8066,7 +8075,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123618504</v>
+        <v>123728604</v>
       </c>
       <c r="B61" t="n">
         <v>98079</v>
@@ -8101,7 +8110,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8125,13 +8134,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>493449</v>
+        <v>493379</v>
       </c>
       <c r="R61" t="n">
-        <v>7009750</v>
+        <v>7009848</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8155,17 +8164,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8197,7 +8206,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123725700</v>
+        <v>123619506</v>
       </c>
       <c r="B62" t="n">
         <v>98079</v>
@@ -8230,19 +8239,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8256,13 +8256,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493341</v>
+        <v>493457</v>
       </c>
       <c r="R62" t="n">
-        <v>7009682</v>
+        <v>7009777</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8286,17 +8286,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -4839,10 +4839,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123616867</v>
+        <v>123617140</v>
       </c>
       <c r="B34" t="n">
-        <v>100257</v>
+        <v>57861</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4855,27 +4855,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4884,13 +4898,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493384</v>
+        <v>493469</v>
       </c>
       <c r="R34" t="n">
-        <v>7009812</v>
+        <v>7009816</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4920,6 +4934,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4951,10 +4970,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617207</v>
+        <v>123617329</v>
       </c>
       <c r="B35" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4967,27 +4986,41 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4996,13 +5029,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493466</v>
+        <v>493431</v>
       </c>
       <c r="R35" t="n">
-        <v>7009777</v>
+        <v>7009773</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5032,6 +5065,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5175,10 +5213,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617329</v>
+        <v>123616867</v>
       </c>
       <c r="B37" t="n">
-        <v>57861</v>
+        <v>100257</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5191,41 +5229,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5234,13 +5258,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493431</v>
+        <v>493384</v>
       </c>
       <c r="R37" t="n">
-        <v>7009773</v>
+        <v>7009812</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5270,11 +5294,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>I flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5306,10 +5325,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617140</v>
+        <v>123617207</v>
       </c>
       <c r="B38" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5322,41 +5341,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5365,13 +5370,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493469</v>
+        <v>493466</v>
       </c>
       <c r="R38" t="n">
-        <v>7009816</v>
+        <v>7009777</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5401,11 +5406,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Observation i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5437,7 +5437,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123726337</v>
+        <v>123725949</v>
       </c>
       <c r="B39" t="n">
         <v>100257</v>
@@ -5487,13 +5487,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493412</v>
+        <v>493389</v>
       </c>
       <c r="R39" t="n">
-        <v>7009647</v>
+        <v>7009683</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123733427</v>
+        <v>123733095</v>
       </c>
       <c r="B40" t="n">
         <v>100257</v>
@@ -5604,13 +5604,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493324</v>
+        <v>493278</v>
       </c>
       <c r="R40" t="n">
-        <v>7009783</v>
+        <v>7009820</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5671,10 +5671,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123725484</v>
+        <v>123725306</v>
       </c>
       <c r="B41" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5687,41 +5687,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5730,13 +5716,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493356</v>
+        <v>493390</v>
       </c>
       <c r="R41" t="n">
-        <v>7009680</v>
+        <v>7009685</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5797,10 +5783,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123727294</v>
+        <v>123725484</v>
       </c>
       <c r="B42" t="n">
-        <v>100257</v>
+        <v>57861</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5813,27 +5799,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5847,13 +5842,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493367</v>
+        <v>493356</v>
       </c>
       <c r="R42" t="n">
-        <v>7009725</v>
+        <v>7009680</v>
       </c>
       <c r="S42" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5914,7 +5909,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123732386</v>
+        <v>123727458</v>
       </c>
       <c r="B43" t="n">
         <v>100257</v>
@@ -5950,7 +5945,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5964,13 +5959,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493374</v>
+        <v>493403</v>
       </c>
       <c r="R43" t="n">
-        <v>7009884</v>
+        <v>7009782</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6031,7 +6026,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123727458</v>
+        <v>123732386</v>
       </c>
       <c r="B44" t="n">
         <v>100257</v>
@@ -6067,7 +6062,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6081,13 +6076,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493403</v>
+        <v>493374</v>
       </c>
       <c r="R44" t="n">
-        <v>7009782</v>
+        <v>7009884</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6148,10 +6143,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123733066</v>
+        <v>123726337</v>
       </c>
       <c r="B45" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6164,21 +6159,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6198,13 +6193,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493280</v>
+        <v>493412</v>
       </c>
       <c r="R45" t="n">
-        <v>7009832</v>
+        <v>7009647</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6265,7 +6260,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123732971</v>
+        <v>123733427</v>
       </c>
       <c r="B46" t="n">
         <v>100257</v>
@@ -6315,13 +6310,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493336</v>
+        <v>493324</v>
       </c>
       <c r="R46" t="n">
-        <v>7009883</v>
+        <v>7009783</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6508,10 +6503,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123725306</v>
+        <v>123730590</v>
       </c>
       <c r="B48" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6524,21 +6519,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6547,19 +6542,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493390</v>
+        <v>493530</v>
       </c>
       <c r="R48" t="n">
-        <v>7009685</v>
+        <v>7009886</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6620,7 +6620,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123725949</v>
+        <v>123727294</v>
       </c>
       <c r="B49" t="n">
         <v>100257</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493389</v>
+        <v>493367</v>
       </c>
       <c r="R49" t="n">
-        <v>7009683</v>
+        <v>7009725</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123725818</v>
+        <v>123730921</v>
       </c>
       <c r="B50" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6753,21 +6753,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493368</v>
+        <v>493438</v>
       </c>
       <c r="R50" t="n">
-        <v>7009687</v>
+        <v>7009868</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6966,7 +6966,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123730921</v>
+        <v>123733352</v>
       </c>
       <c r="B52" t="n">
         <v>100257</v>
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493438</v>
+        <v>493302</v>
       </c>
       <c r="R52" t="n">
-        <v>7009868</v>
+        <v>7009788</v>
       </c>
       <c r="S52" t="n">
         <v>11</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7083,10 +7083,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123733095</v>
+        <v>123733066</v>
       </c>
       <c r="B53" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7133,13 +7133,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493278</v>
+        <v>493280</v>
       </c>
       <c r="R53" t="n">
-        <v>7009820</v>
+        <v>7009832</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123730590</v>
+        <v>123726856</v>
       </c>
       <c r="B54" t="n">
         <v>100257</v>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493530</v>
+        <v>493371</v>
       </c>
       <c r="R54" t="n">
-        <v>7009886</v>
+        <v>7009706</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7317,7 +7317,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123733352</v>
+        <v>123732971</v>
       </c>
       <c r="B55" t="n">
         <v>100257</v>
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493302</v>
+        <v>493336</v>
       </c>
       <c r="R55" t="n">
-        <v>7009788</v>
+        <v>7009883</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123726856</v>
+        <v>123725818</v>
       </c>
       <c r="B56" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7450,21 +7450,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7484,13 +7484,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493371</v>
+        <v>493368</v>
       </c>
       <c r="R56" t="n">
-        <v>7009706</v>
+        <v>7009687</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123730088</v>
+        <v>123618504</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493472</v>
+        <v>493449</v>
       </c>
       <c r="R57" t="n">
-        <v>7009838</v>
+        <v>7009750</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7640,17 +7640,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123732177</v>
+        <v>123725700</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493430</v>
+        <v>493341</v>
       </c>
       <c r="R58" t="n">
-        <v>7009898</v>
+        <v>7009682</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7813,7 +7813,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123725700</v>
+        <v>123619506</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -7846,19 +7846,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -7872,13 +7863,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493341</v>
+        <v>493457</v>
       </c>
       <c r="R59" t="n">
-        <v>7009682</v>
+        <v>7009777</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7902,17 +7893,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7944,7 +7935,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123618504</v>
+        <v>123730088</v>
       </c>
       <c r="B60" t="n">
         <v>98079</v>
@@ -7979,7 +7970,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8003,10 +7994,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493449</v>
+        <v>493472</v>
       </c>
       <c r="R60" t="n">
-        <v>7009750</v>
+        <v>7009838</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -8033,17 +8024,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8057,7 +8048,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8206,7 +8197,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123619506</v>
+        <v>123732177</v>
       </c>
       <c r="B62" t="n">
         <v>98079</v>
@@ -8239,10 +8230,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8256,13 +8256,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493457</v>
+        <v>493430</v>
       </c>
       <c r="R62" t="n">
-        <v>7009777</v>
+        <v>7009898</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8286,17 +8286,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 300 st plantor och 1 st vinterståndare på en yta av ca 4 x 0,5 m2 inom ca 6 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -7551,7 +7551,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123619506</v>
+        <v>123618504</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -7584,10 +7584,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -7601,13 +7610,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493457</v>
+        <v>493449</v>
       </c>
       <c r="R57" t="n">
-        <v>7009777</v>
+        <v>7009750</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7641,7 +7650,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7673,7 +7682,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123730088</v>
+        <v>123619506</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -7706,19 +7715,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493472</v>
+        <v>493457</v>
       </c>
       <c r="R58" t="n">
-        <v>7009838</v>
+        <v>7009777</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7762,17 +7762,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
+          <t>Minst 250 st plantor och 21 st vinterståndare på en yta av ca 2 m2 på och kring en gammal överväxt stubbe. De flesta plantorna finns kring stubben. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7804,7 +7804,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123725700</v>
+        <v>123730088</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493341</v>
+        <v>493472</v>
       </c>
       <c r="R59" t="n">
-        <v>7009682</v>
+        <v>7009838</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
+          <t>Minst 330 st plantor och 4 st vinterståndare på en yta av ca 8 m2. Fyndplatsen finns i gammal granskog/barrblandskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7935,7 +7935,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123618504</v>
+        <v>123728604</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7994,13 +7994,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493449</v>
+        <v>493379</v>
       </c>
       <c r="R60" t="n">
-        <v>7009750</v>
+        <v>7009848</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8024,17 +8024,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 340 st plantor och 7 st vinterståndare på en yta av ca 3 x 1 m2 inom ca 4 meters radie från fyndplatsens koordinatpunkt vid en nyligen hackspettsbearbetad stående död gran (se bild). Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8066,7 +8066,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123728604</v>
+        <v>123725700</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>493379</v>
+        <v>493341</v>
       </c>
       <c r="R61" t="n">
-        <v>7009848</v>
+        <v>7009682</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 410 st plantor och 8 st vinterståndare på en yta av ca 5 x 1 m2 inom ca 5 meters radie från fyndplatsens koordinatpunkt. Fyndplatsen finns i gammal granskog.</t>
+          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8581,7 +8581,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124503013</v>
+        <v>124499041</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -8626,13 +8626,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493421</v>
+        <v>493239</v>
       </c>
       <c r="R65" t="n">
-        <v>7009797</v>
+        <v>7009796</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8825,7 +8825,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124499041</v>
+        <v>124503013</v>
       </c>
       <c r="B67" t="n">
         <v>100279</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493239</v>
+        <v>493421</v>
       </c>
       <c r="R67" t="n">
-        <v>7009796</v>
+        <v>7009797</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124498649</v>
+        <v>124501251</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493256</v>
+        <v>493356</v>
       </c>
       <c r="R68" t="n">
-        <v>7009831</v>
+        <v>7009863</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124501251</v>
+        <v>124503702</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493356</v>
+        <v>493353</v>
       </c>
       <c r="R69" t="n">
-        <v>7009863</v>
+        <v>7009865</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9219,7 +9219,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124503702</v>
+        <v>124498649</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493353</v>
+        <v>493256</v>
       </c>
       <c r="R70" t="n">
-        <v>7009865</v>
+        <v>7009831</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8328,7 +8328,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124499923</v>
+        <v>124503013</v>
       </c>
       <c r="B63" t="n">
         <v>100279</v>
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493294</v>
+        <v>493421</v>
       </c>
       <c r="R63" t="n">
-        <v>7009813</v>
+        <v>7009797</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8703,7 +8703,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124500585</v>
+        <v>124499923</v>
       </c>
       <c r="B66" t="n">
         <v>100279</v>
@@ -8748,13 +8748,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493320</v>
+        <v>493294</v>
       </c>
       <c r="R66" t="n">
-        <v>7009826</v>
+        <v>7009813</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8825,7 +8825,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124503013</v>
+        <v>124500585</v>
       </c>
       <c r="B67" t="n">
         <v>100279</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493421</v>
+        <v>493320</v>
       </c>
       <c r="R67" t="n">
-        <v>7009797</v>
+        <v>7009826</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124501251</v>
+        <v>124503702</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493356</v>
+        <v>493353</v>
       </c>
       <c r="R68" t="n">
-        <v>7009863</v>
+        <v>7009865</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124503702</v>
+        <v>124498649</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493353</v>
+        <v>493256</v>
       </c>
       <c r="R69" t="n">
-        <v>7009865</v>
+        <v>7009831</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9219,7 +9219,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124498649</v>
+        <v>124501251</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493256</v>
+        <v>493356</v>
       </c>
       <c r="R70" t="n">
-        <v>7009831</v>
+        <v>7009863</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8328,7 +8328,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124503013</v>
+        <v>124500585</v>
       </c>
       <c r="B63" t="n">
         <v>100279</v>
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493421</v>
+        <v>493320</v>
       </c>
       <c r="R63" t="n">
-        <v>7009797</v>
+        <v>7009826</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8450,10 +8450,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124499433</v>
+        <v>124503013</v>
       </c>
       <c r="B64" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8466,36 +8466,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8504,13 +8495,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493186</v>
+        <v>493421</v>
       </c>
       <c r="R64" t="n">
-        <v>7009781</v>
+        <v>7009797</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8539,7 +8530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8549,7 +8540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8563,7 +8554,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8581,10 +8572,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124499041</v>
+        <v>124499433</v>
       </c>
       <c r="B65" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8597,27 +8588,36 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493239</v>
+        <v>493186</v>
       </c>
       <c r="R65" t="n">
-        <v>7009796</v>
+        <v>7009781</v>
       </c>
       <c r="S65" t="n">
         <v>8</v>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8825,7 +8825,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124500585</v>
+        <v>124499041</v>
       </c>
       <c r="B67" t="n">
         <v>100279</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493320</v>
+        <v>493239</v>
       </c>
       <c r="R67" t="n">
-        <v>7009826</v>
+        <v>7009796</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124503702</v>
+        <v>124498649</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493353</v>
+        <v>493256</v>
       </c>
       <c r="R68" t="n">
-        <v>7009865</v>
+        <v>7009831</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124498649</v>
+        <v>124503702</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493256</v>
+        <v>493353</v>
       </c>
       <c r="R69" t="n">
-        <v>7009831</v>
+        <v>7009865</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8328,7 +8328,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124500585</v>
+        <v>124499923</v>
       </c>
       <c r="B63" t="n">
         <v>100279</v>
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493320</v>
+        <v>493294</v>
       </c>
       <c r="R63" t="n">
-        <v>7009826</v>
+        <v>7009813</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8450,7 +8450,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124503013</v>
+        <v>124500585</v>
       </c>
       <c r="B64" t="n">
         <v>100279</v>
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493421</v>
+        <v>493320</v>
       </c>
       <c r="R64" t="n">
-        <v>7009797</v>
+        <v>7009826</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8572,10 +8572,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124499433</v>
+        <v>124503013</v>
       </c>
       <c r="B65" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8588,36 +8588,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8626,13 +8617,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493186</v>
+        <v>493421</v>
       </c>
       <c r="R65" t="n">
-        <v>7009781</v>
+        <v>7009797</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8661,7 +8652,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8671,7 +8662,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8685,7 +8676,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8703,10 +8694,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124499923</v>
+        <v>124499433</v>
       </c>
       <c r="B66" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8719,27 +8710,36 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493294</v>
+        <v>493186</v>
       </c>
       <c r="R66" t="n">
-        <v>7009813</v>
+        <v>7009781</v>
       </c>
       <c r="S66" t="n">
         <v>8</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124503702</v>
+        <v>124501251</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493353</v>
+        <v>493356</v>
       </c>
       <c r="R69" t="n">
-        <v>7009865</v>
+        <v>7009863</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9219,7 +9219,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124501251</v>
+        <v>124503702</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493356</v>
+        <v>493353</v>
       </c>
       <c r="R70" t="n">
-        <v>7009863</v>
+        <v>7009865</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8328,10 +8328,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124499923</v>
+        <v>124499433</v>
       </c>
       <c r="B63" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8344,27 +8344,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8373,10 +8382,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493294</v>
+        <v>493186</v>
       </c>
       <c r="R63" t="n">
-        <v>7009813</v>
+        <v>7009781</v>
       </c>
       <c r="S63" t="n">
         <v>8</v>
@@ -8408,7 +8417,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8418,7 +8427,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8450,7 +8459,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124500585</v>
+        <v>124499041</v>
       </c>
       <c r="B64" t="n">
         <v>100279</v>
@@ -8495,13 +8504,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493320</v>
+        <v>493239</v>
       </c>
       <c r="R64" t="n">
-        <v>7009826</v>
+        <v>7009796</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8530,7 +8539,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8540,7 +8549,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8694,10 +8703,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124499433</v>
+        <v>124499923</v>
       </c>
       <c r="B66" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8710,36 +8719,27 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493186</v>
+        <v>493294</v>
       </c>
       <c r="R66" t="n">
-        <v>7009781</v>
+        <v>7009813</v>
       </c>
       <c r="S66" t="n">
         <v>8</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8825,7 +8825,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124499041</v>
+        <v>124500585</v>
       </c>
       <c r="B67" t="n">
         <v>100279</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493239</v>
+        <v>493320</v>
       </c>
       <c r="R67" t="n">
-        <v>7009796</v>
+        <v>7009826</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124498649</v>
+        <v>124501251</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493256</v>
+        <v>493356</v>
       </c>
       <c r="R68" t="n">
-        <v>7009831</v>
+        <v>7009863</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124501251</v>
+        <v>124498649</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493356</v>
+        <v>493256</v>
       </c>
       <c r="R69" t="n">
-        <v>7009863</v>
+        <v>7009831</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8328,10 +8328,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124499433</v>
+        <v>124499041</v>
       </c>
       <c r="B63" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8344,36 +8344,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8382,10 +8373,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493186</v>
+        <v>493239</v>
       </c>
       <c r="R63" t="n">
-        <v>7009781</v>
+        <v>7009796</v>
       </c>
       <c r="S63" t="n">
         <v>8</v>
@@ -8417,7 +8408,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8427,7 +8418,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8459,7 +8450,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124499041</v>
+        <v>124499923</v>
       </c>
       <c r="B64" t="n">
         <v>100279</v>
@@ -8504,10 +8495,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493239</v>
+        <v>493294</v>
       </c>
       <c r="R64" t="n">
-        <v>7009796</v>
+        <v>7009813</v>
       </c>
       <c r="S64" t="n">
         <v>8</v>
@@ -8539,7 +8530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8549,7 +8540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8581,7 +8572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124503013</v>
+        <v>124500585</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -8626,13 +8617,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493421</v>
+        <v>493320</v>
       </c>
       <c r="R65" t="n">
-        <v>7009797</v>
+        <v>7009826</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8661,7 +8652,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8671,7 +8662,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8685,7 +8676,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8703,7 +8694,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124499923</v>
+        <v>124503013</v>
       </c>
       <c r="B66" t="n">
         <v>100279</v>
@@ -8748,13 +8739,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493294</v>
+        <v>493421</v>
       </c>
       <c r="R66" t="n">
-        <v>7009813</v>
+        <v>7009797</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8783,7 +8774,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8793,7 +8784,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8807,7 +8798,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8825,10 +8816,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124500585</v>
+        <v>124499433</v>
       </c>
       <c r="B67" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8841,27 +8832,36 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493320</v>
+        <v>493186</v>
       </c>
       <c r="R67" t="n">
-        <v>7009826</v>
+        <v>7009781</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124501251</v>
+        <v>124503702</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493356</v>
+        <v>493353</v>
       </c>
       <c r="R68" t="n">
-        <v>7009863</v>
+        <v>7009865</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124498649</v>
+        <v>124501251</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493256</v>
+        <v>493356</v>
       </c>
       <c r="R69" t="n">
-        <v>7009831</v>
+        <v>7009863</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9219,7 +9219,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124503702</v>
+        <v>124498649</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493353</v>
+        <v>493256</v>
       </c>
       <c r="R70" t="n">
-        <v>7009865</v>
+        <v>7009831</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8328,7 +8328,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124499041</v>
+        <v>124499923</v>
       </c>
       <c r="B63" t="n">
         <v>100279</v>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493239</v>
+        <v>493294</v>
       </c>
       <c r="R63" t="n">
-        <v>7009796</v>
+        <v>7009813</v>
       </c>
       <c r="S63" t="n">
         <v>8</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8450,7 +8450,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124499923</v>
+        <v>124500585</v>
       </c>
       <c r="B64" t="n">
         <v>100279</v>
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493294</v>
+        <v>493320</v>
       </c>
       <c r="R64" t="n">
-        <v>7009813</v>
+        <v>7009826</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8572,7 +8572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124500585</v>
+        <v>124503013</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -8617,13 +8617,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493320</v>
+        <v>493421</v>
       </c>
       <c r="R65" t="n">
-        <v>7009826</v>
+        <v>7009797</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8694,10 +8694,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124503013</v>
+        <v>124499433</v>
       </c>
       <c r="B66" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8710,27 +8710,36 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8739,13 +8748,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493421</v>
+        <v>493186</v>
       </c>
       <c r="R66" t="n">
-        <v>7009797</v>
+        <v>7009781</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8774,7 +8783,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8784,7 +8793,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8798,7 +8807,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8816,10 +8825,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124499433</v>
+        <v>124499041</v>
       </c>
       <c r="B67" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8832,36 +8841,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8870,10 +8870,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493186</v>
+        <v>493239</v>
       </c>
       <c r="R67" t="n">
-        <v>7009781</v>
+        <v>7009796</v>
       </c>
       <c r="S67" t="n">
         <v>8</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124503702</v>
+        <v>124501251</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493353</v>
+        <v>493356</v>
       </c>
       <c r="R68" t="n">
-        <v>7009865</v>
+        <v>7009863</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124501251</v>
+        <v>124498649</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493356</v>
+        <v>493256</v>
       </c>
       <c r="R69" t="n">
-        <v>7009863</v>
+        <v>7009831</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9219,7 +9219,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124498649</v>
+        <v>124503702</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493256</v>
+        <v>493353</v>
       </c>
       <c r="R70" t="n">
-        <v>7009831</v>
+        <v>7009865</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8450,7 +8450,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124500585</v>
+        <v>124503013</v>
       </c>
       <c r="B64" t="n">
         <v>100279</v>
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493320</v>
+        <v>493421</v>
       </c>
       <c r="R64" t="n">
-        <v>7009826</v>
+        <v>7009797</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8572,7 +8572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124503013</v>
+        <v>124500585</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -8617,13 +8617,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493421</v>
+        <v>493320</v>
       </c>
       <c r="R65" t="n">
-        <v>7009797</v>
+        <v>7009826</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124501251</v>
+        <v>124498649</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493356</v>
+        <v>493256</v>
       </c>
       <c r="R68" t="n">
-        <v>7009863</v>
+        <v>7009831</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124498649</v>
+        <v>124501251</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493256</v>
+        <v>493356</v>
       </c>
       <c r="R69" t="n">
-        <v>7009831</v>
+        <v>7009863</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8328,7 +8328,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124499923</v>
+        <v>124500585</v>
       </c>
       <c r="B63" t="n">
         <v>100279</v>
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493294</v>
+        <v>493320</v>
       </c>
       <c r="R63" t="n">
-        <v>7009813</v>
+        <v>7009826</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8450,7 +8450,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124503013</v>
+        <v>124499041</v>
       </c>
       <c r="B64" t="n">
         <v>100279</v>
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493421</v>
+        <v>493239</v>
       </c>
       <c r="R64" t="n">
-        <v>7009797</v>
+        <v>7009796</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8572,7 +8572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124500585</v>
+        <v>124499923</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -8617,13 +8617,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493320</v>
+        <v>493294</v>
       </c>
       <c r="R65" t="n">
-        <v>7009826</v>
+        <v>7009813</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8694,10 +8694,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124499433</v>
+        <v>124503013</v>
       </c>
       <c r="B66" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8710,36 +8710,27 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8748,13 +8739,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493186</v>
+        <v>493421</v>
       </c>
       <c r="R66" t="n">
-        <v>7009781</v>
+        <v>7009797</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8783,7 +8774,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8793,7 +8784,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8807,7 +8798,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8825,10 +8816,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124499041</v>
+        <v>124499433</v>
       </c>
       <c r="B67" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8841,27 +8832,36 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8870,10 +8870,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493239</v>
+        <v>493186</v>
       </c>
       <c r="R67" t="n">
-        <v>7009796</v>
+        <v>7009781</v>
       </c>
       <c r="S67" t="n">
         <v>8</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124501251</v>
+        <v>124503702</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493356</v>
+        <v>493353</v>
       </c>
       <c r="R69" t="n">
-        <v>7009863</v>
+        <v>7009865</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9219,7 +9219,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124503702</v>
+        <v>124501251</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493353</v>
+        <v>493356</v>
       </c>
       <c r="R70" t="n">
-        <v>7009865</v>
+        <v>7009863</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8328,7 +8328,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124500585</v>
+        <v>124499923</v>
       </c>
       <c r="B63" t="n">
         <v>100279</v>
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493320</v>
+        <v>493294</v>
       </c>
       <c r="R63" t="n">
-        <v>7009826</v>
+        <v>7009813</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8450,7 +8450,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124499041</v>
+        <v>124500585</v>
       </c>
       <c r="B64" t="n">
         <v>100279</v>
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493239</v>
+        <v>493320</v>
       </c>
       <c r="R64" t="n">
-        <v>7009796</v>
+        <v>7009826</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8572,10 +8572,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124499923</v>
+        <v>124499433</v>
       </c>
       <c r="B65" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8588,27 +8588,36 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8617,10 +8626,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493294</v>
+        <v>493186</v>
       </c>
       <c r="R65" t="n">
-        <v>7009813</v>
+        <v>7009781</v>
       </c>
       <c r="S65" t="n">
         <v>8</v>
@@ -8652,7 +8661,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8662,7 +8671,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8694,7 +8703,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124503013</v>
+        <v>124499041</v>
       </c>
       <c r="B66" t="n">
         <v>100279</v>
@@ -8739,13 +8748,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493421</v>
+        <v>493239</v>
       </c>
       <c r="R66" t="n">
-        <v>7009797</v>
+        <v>7009796</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8774,7 +8783,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8784,7 +8793,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8798,7 +8807,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8816,10 +8825,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124499433</v>
+        <v>124503013</v>
       </c>
       <c r="B67" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8832,36 +8841,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493186</v>
+        <v>493421</v>
       </c>
       <c r="R67" t="n">
-        <v>7009781</v>
+        <v>7009797</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124498649</v>
+        <v>124501251</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493256</v>
+        <v>493356</v>
       </c>
       <c r="R68" t="n">
-        <v>7009831</v>
+        <v>7009863</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124503702</v>
+        <v>124498649</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493353</v>
+        <v>493256</v>
       </c>
       <c r="R69" t="n">
-        <v>7009865</v>
+        <v>7009831</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9219,7 +9219,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124501251</v>
+        <v>124503702</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493356</v>
+        <v>493353</v>
       </c>
       <c r="R70" t="n">
-        <v>7009863</v>
+        <v>7009865</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8450,7 +8450,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124500585</v>
+        <v>124503013</v>
       </c>
       <c r="B64" t="n">
         <v>100279</v>
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493320</v>
+        <v>493421</v>
       </c>
       <c r="R64" t="n">
-        <v>7009826</v>
+        <v>7009797</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8572,10 +8572,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124499433</v>
+        <v>124500585</v>
       </c>
       <c r="B65" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8588,36 +8588,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8626,13 +8617,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493186</v>
+        <v>493320</v>
       </c>
       <c r="R65" t="n">
-        <v>7009781</v>
+        <v>7009826</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8661,7 +8652,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8671,7 +8662,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8703,10 +8694,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124499041</v>
+        <v>124499433</v>
       </c>
       <c r="B66" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8719,27 +8710,36 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493239</v>
+        <v>493186</v>
       </c>
       <c r="R66" t="n">
-        <v>7009796</v>
+        <v>7009781</v>
       </c>
       <c r="S66" t="n">
         <v>8</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8825,7 +8825,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124503013</v>
+        <v>124499041</v>
       </c>
       <c r="B67" t="n">
         <v>100279</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493421</v>
+        <v>493239</v>
       </c>
       <c r="R67" t="n">
-        <v>7009797</v>
+        <v>7009796</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124498649</v>
+        <v>124503702</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493256</v>
+        <v>493353</v>
       </c>
       <c r="R69" t="n">
-        <v>7009831</v>
+        <v>7009865</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9219,7 +9219,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124503702</v>
+        <v>124498649</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493353</v>
+        <v>493256</v>
       </c>
       <c r="R70" t="n">
-        <v>7009865</v>
+        <v>7009831</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8450,10 +8450,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124503013</v>
+        <v>124499433</v>
       </c>
       <c r="B64" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8466,27 +8466,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8495,13 +8504,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493421</v>
+        <v>493186</v>
       </c>
       <c r="R64" t="n">
-        <v>7009797</v>
+        <v>7009781</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8530,7 +8539,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8540,7 +8549,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8554,7 +8563,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8572,7 +8581,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124500585</v>
+        <v>124499041</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -8617,13 +8626,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493320</v>
+        <v>493239</v>
       </c>
       <c r="R65" t="n">
-        <v>7009826</v>
+        <v>7009796</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8652,7 +8661,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8662,7 +8671,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8694,10 +8703,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124499433</v>
+        <v>124503013</v>
       </c>
       <c r="B66" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8710,36 +8719,27 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8748,13 +8748,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493186</v>
+        <v>493421</v>
       </c>
       <c r="R66" t="n">
-        <v>7009781</v>
+        <v>7009797</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8825,7 +8825,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124499041</v>
+        <v>124500585</v>
       </c>
       <c r="B67" t="n">
         <v>100279</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493239</v>
+        <v>493320</v>
       </c>
       <c r="R67" t="n">
-        <v>7009796</v>
+        <v>7009826</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124501251</v>
+        <v>124503702</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493356</v>
+        <v>493353</v>
       </c>
       <c r="R68" t="n">
-        <v>7009863</v>
+        <v>7009865</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124503702</v>
+        <v>124501251</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493353</v>
+        <v>493356</v>
       </c>
       <c r="R69" t="n">
-        <v>7009865</v>
+        <v>7009863</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8581,7 +8581,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124499041</v>
+        <v>124500585</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -8626,13 +8626,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493239</v>
+        <v>493320</v>
       </c>
       <c r="R65" t="n">
-        <v>7009796</v>
+        <v>7009826</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8703,7 +8703,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124503013</v>
+        <v>124499041</v>
       </c>
       <c r="B66" t="n">
         <v>100279</v>
@@ -8748,13 +8748,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493421</v>
+        <v>493239</v>
       </c>
       <c r="R66" t="n">
-        <v>7009797</v>
+        <v>7009796</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8825,7 +8825,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124500585</v>
+        <v>124503013</v>
       </c>
       <c r="B67" t="n">
         <v>100279</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493320</v>
+        <v>493421</v>
       </c>
       <c r="R67" t="n">
-        <v>7009826</v>
+        <v>7009797</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124503702</v>
+        <v>124501251</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493353</v>
+        <v>493356</v>
       </c>
       <c r="R68" t="n">
-        <v>7009865</v>
+        <v>7009863</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124501251</v>
+        <v>124498649</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493356</v>
+        <v>493256</v>
       </c>
       <c r="R69" t="n">
-        <v>7009863</v>
+        <v>7009831</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9219,7 +9219,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124498649</v>
+        <v>124503702</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493256</v>
+        <v>493353</v>
       </c>
       <c r="R70" t="n">
-        <v>7009831</v>
+        <v>7009865</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 5 plantor inom ca 0,2 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8328,7 +8328,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124499923</v>
+        <v>124503013</v>
       </c>
       <c r="B63" t="n">
         <v>100279</v>
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493294</v>
+        <v>493421</v>
       </c>
       <c r="R63" t="n">
-        <v>7009813</v>
+        <v>7009797</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8450,10 +8450,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124499433</v>
+        <v>124500585</v>
       </c>
       <c r="B64" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8466,36 +8466,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8504,13 +8495,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493186</v>
+        <v>493320</v>
       </c>
       <c r="R64" t="n">
-        <v>7009781</v>
+        <v>7009826</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8539,7 +8530,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8549,7 +8540,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8581,7 +8572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124500585</v>
+        <v>124499041</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -8626,13 +8617,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493320</v>
+        <v>493239</v>
       </c>
       <c r="R65" t="n">
-        <v>7009826</v>
+        <v>7009796</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8661,7 +8652,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8671,7 +8662,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8703,7 +8694,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124499041</v>
+        <v>124499923</v>
       </c>
       <c r="B66" t="n">
         <v>100279</v>
@@ -8748,10 +8739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493239</v>
+        <v>493294</v>
       </c>
       <c r="R66" t="n">
-        <v>7009796</v>
+        <v>7009813</v>
       </c>
       <c r="S66" t="n">
         <v>8</v>
@@ -8783,7 +8774,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8793,7 +8784,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8825,10 +8816,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124503013</v>
+        <v>124499433</v>
       </c>
       <c r="B67" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8841,27 +8832,36 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493421</v>
+        <v>493186</v>
       </c>
       <c r="R67" t="n">
-        <v>7009797</v>
+        <v>7009781</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8947,7 +8947,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124501251</v>
+        <v>124498649</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493356</v>
+        <v>493256</v>
       </c>
       <c r="R68" t="n">
-        <v>7009863</v>
+        <v>7009831</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124498649</v>
+        <v>124501251</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9137,13 +9137,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493256</v>
+        <v>493356</v>
       </c>
       <c r="R69" t="n">
-        <v>7009831</v>
+        <v>7009863</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>Minst 50 plantor och 2 vinterståndare inom ca 1,5 m2 i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -8450,10 +8450,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124500585</v>
+        <v>124499433</v>
       </c>
       <c r="B64" t="n">
-        <v>100279</v>
+        <v>57883</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8466,27 +8466,36 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8495,13 +8504,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493320</v>
+        <v>493186</v>
       </c>
       <c r="R64" t="n">
-        <v>7009826</v>
+        <v>7009781</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8530,7 +8539,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8540,7 +8549,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8572,7 +8581,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124499041</v>
+        <v>124499923</v>
       </c>
       <c r="B65" t="n">
         <v>100279</v>
@@ -8617,10 +8626,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493239</v>
+        <v>493294</v>
       </c>
       <c r="R65" t="n">
-        <v>7009796</v>
+        <v>7009813</v>
       </c>
       <c r="S65" t="n">
         <v>8</v>
@@ -8652,7 +8661,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8662,7 +8671,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8694,7 +8703,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124499923</v>
+        <v>124499041</v>
       </c>
       <c r="B66" t="n">
         <v>100279</v>
@@ -8739,10 +8748,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493294</v>
+        <v>493239</v>
       </c>
       <c r="R66" t="n">
-        <v>7009813</v>
+        <v>7009796</v>
       </c>
       <c r="S66" t="n">
         <v>8</v>
@@ -8774,7 +8783,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8784,7 +8793,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8816,10 +8825,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124499433</v>
+        <v>124500585</v>
       </c>
       <c r="B67" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8832,36 +8841,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493186</v>
+        <v>493320</v>
       </c>
       <c r="R67" t="n">
-        <v>7009781</v>
+        <v>7009826</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9353,6 +9353,360 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125757252</v>
+      </c>
+      <c r="B71" t="n">
+        <v>100506</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>493446</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7009874</v>
+      </c>
+      <c r="S71" t="n">
+        <v>8</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125757311</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>493445</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7009875</v>
+      </c>
+      <c r="S72" t="n">
+        <v>8</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor inom ca 0,2 m2 yta i gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125755405</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58083</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Brynjelägden, Brynjelägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>493404</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7009887</v>
+      </c>
+      <c r="S73" t="n">
+        <v>50</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -9358,7 +9358,7 @@
         <v>125757252</v>
       </c>
       <c r="B71" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>125757311</v>
       </c>
       <c r="B72" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -9358,7 +9358,7 @@
         <v>125757252</v>
       </c>
       <c r="B71" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>125757311</v>
       </c>
       <c r="B72" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>125755405</v>
       </c>
       <c r="B73" t="n">
-        <v>58083</v>
+        <v>58084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -9358,7 +9358,7 @@
         <v>125757252</v>
       </c>
       <c r="B71" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>125757311</v>
       </c>
       <c r="B72" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -9358,7 +9358,7 @@
         <v>125757252</v>
       </c>
       <c r="B71" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>125757311</v>
       </c>
       <c r="B72" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -9358,7 +9358,7 @@
         <v>125757252</v>
       </c>
       <c r="B71" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>125757311</v>
       </c>
       <c r="B72" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>125755405</v>
       </c>
       <c r="B73" t="n">
-        <v>58084</v>
+        <v>58085</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -9358,7 +9358,7 @@
         <v>125757252</v>
       </c>
       <c r="B71" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>125757311</v>
       </c>
       <c r="B72" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -9358,7 +9358,7 @@
         <v>125757252</v>
       </c>
       <c r="B71" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>125757311</v>
       </c>
       <c r="B72" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -9358,7 +9358,7 @@
         <v>125757252</v>
       </c>
       <c r="B71" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>125757311</v>
       </c>
       <c r="B72" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>125755405</v>
       </c>
       <c r="B73" t="n">
-        <v>58085</v>
+        <v>58089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 5626-2025 artfynd.xlsx
+++ b/artfynd/A 5626-2025 artfynd.xlsx
@@ -9358,7 +9358,7 @@
         <v>125757252</v>
       </c>
       <c r="B71" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>125757311</v>
       </c>
       <c r="B72" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
